--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -1976,10 +1976,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125201638</v>
+        <v>125205942</v>
       </c>
       <c r="B14" t="n">
-        <v>78842</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1992,34 +1992,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>784464</v>
+        <v>784340</v>
       </c>
       <c r="R14" t="n">
-        <v>7286498</v>
+        <v>7286230</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,22 +2066,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125205942</v>
+        <v>125201638</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>78842</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,34 +2094,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>784340</v>
+        <v>784464</v>
       </c>
       <c r="R15" t="n">
-        <v>7286230</v>
+        <v>7286498</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,12 +2168,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -2180,10 +2180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125205935</v>
+        <v>125201648</v>
       </c>
       <c r="B16" t="n">
-        <v>91299</v>
+        <v>91457</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2192,38 +2192,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>784264</v>
+        <v>784333</v>
       </c>
       <c r="R16" t="n">
-        <v>7286244</v>
+        <v>7286210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,6 +2258,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gran bark kvar</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2270,22 +2275,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125205939</v>
+        <v>125205935</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>91299</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2294,25 +2299,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2322,10 +2327,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>784306</v>
+        <v>784264</v>
       </c>
       <c r="R17" t="n">
-        <v>7286218</v>
+        <v>7286244</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2384,10 +2389,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125205937</v>
+        <v>125205939</v>
       </c>
       <c r="B18" t="n">
-        <v>96979</v>
+        <v>57883</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2400,21 +2405,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,10 +2429,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>784359</v>
+        <v>784306</v>
       </c>
       <c r="R18" t="n">
-        <v>7286440</v>
+        <v>7286218</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,7 +2491,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125205938</v>
+        <v>125205937</v>
       </c>
       <c r="B19" t="n">
         <v>96979</v>
@@ -2526,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>784387</v>
+        <v>784359</v>
       </c>
       <c r="R19" t="n">
-        <v>7286256</v>
+        <v>7286440</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,10 +2593,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125201648</v>
+        <v>125205938</v>
       </c>
       <c r="B20" t="n">
-        <v>91457</v>
+        <v>96979</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2600,38 +2605,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>784333</v>
+        <v>784387</v>
       </c>
       <c r="R20" t="n">
-        <v>7286210</v>
+        <v>7286256</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,11 +2671,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gran bark kvar</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2683,22 +2683,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125201677</v>
+        <v>125205961</v>
       </c>
       <c r="B21" t="n">
-        <v>82597</v>
+        <v>96227</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2707,38 +2707,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>784276</v>
+        <v>784461</v>
       </c>
       <c r="R21" t="n">
-        <v>7286135</v>
+        <v>7286446</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,22 +2785,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125205961</v>
+        <v>125201677</v>
       </c>
       <c r="B22" t="n">
-        <v>96227</v>
+        <v>82597</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,38 +2809,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>784461</v>
+        <v>784276</v>
       </c>
       <c r="R22" t="n">
-        <v>7286446</v>
+        <v>7286135</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,12 +2887,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125205958</v>
+        <v>125205925</v>
       </c>
       <c r="B2" t="n">
-        <v>74893</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>784424</v>
+        <v>784312</v>
       </c>
       <c r="R2" t="n">
-        <v>7286482</v>
+        <v>7286305</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,9 +764,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125205928</v>
+        <v>125201648</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>91457</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +815,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784295</v>
+        <v>784333</v>
       </c>
       <c r="R3" t="n">
-        <v>7286331</v>
+        <v>7286210</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,19 +876,14 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:01</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gran bark kvar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,12 +898,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -999,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125205956</v>
+        <v>125205939</v>
       </c>
       <c r="B5" t="n">
-        <v>56965</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,16 +1028,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1033,24 +1046,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784280</v>
+        <v>784306</v>
       </c>
       <c r="R5" t="n">
-        <v>7286150</v>
+        <v>7286218</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,19 +1085,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125205950</v>
+        <v>125205921</v>
       </c>
       <c r="B6" t="n">
-        <v>82597</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1126,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784389</v>
+        <v>784282</v>
       </c>
       <c r="R6" t="n">
-        <v>7286301</v>
+        <v>7286280</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125205944</v>
+        <v>125205931</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,34 +1232,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784323</v>
+        <v>784313</v>
       </c>
       <c r="R7" t="n">
-        <v>7286284</v>
+        <v>7286297</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,9 +1297,24 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125205931</v>
+        <v>125205936</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,46 +1455,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>784313</v>
+        <v>784312</v>
       </c>
       <c r="R9" t="n">
-        <v>7286297</v>
+        <v>7286355</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,24 +1516,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,7 +1545,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125205936</v>
+        <v>125205937</v>
       </c>
       <c r="B10" t="n">
         <v>96979</v>
@@ -1590,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784312</v>
+        <v>784359</v>
       </c>
       <c r="R10" t="n">
-        <v>7286355</v>
+        <v>7286440</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125205941</v>
+        <v>125201677</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,34 +1663,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784331</v>
+        <v>784276</v>
       </c>
       <c r="R11" t="n">
-        <v>7286390</v>
+        <v>7286135</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,22 +1737,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125205951</v>
+        <v>125205928</v>
       </c>
       <c r="B12" t="n">
-        <v>82597</v>
+        <v>57666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,34 +1765,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784382</v>
+        <v>784295</v>
       </c>
       <c r="R12" t="n">
-        <v>7286215</v>
+        <v>7286331</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,9 +1830,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125205953</v>
+        <v>125205961</v>
       </c>
       <c r="B13" t="n">
-        <v>56965</v>
+        <v>96227</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,42 +1885,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102954</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>784304</v>
+        <v>784461</v>
       </c>
       <c r="R13" t="n">
-        <v>7286278</v>
+        <v>7286446</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,19 +1942,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1976,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125205942</v>
+        <v>125205935</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1992,21 +1987,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2016,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>784340</v>
+        <v>784264</v>
       </c>
       <c r="R14" t="n">
-        <v>7286230</v>
+        <v>7286244</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125201638</v>
+        <v>125205951</v>
       </c>
       <c r="B15" t="n">
-        <v>78842</v>
+        <v>82597</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,34 +2089,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>784464</v>
+        <v>784382</v>
       </c>
       <c r="R15" t="n">
-        <v>7286498</v>
+        <v>7286215</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,22 +2163,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125201648</v>
+        <v>125205959</v>
       </c>
       <c r="B16" t="n">
-        <v>91457</v>
+        <v>96227</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2192,38 +2187,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>784333</v>
+        <v>784478</v>
       </c>
       <c r="R16" t="n">
-        <v>7286210</v>
+        <v>7286475</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,11 +2253,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gran bark kvar</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2275,22 +2265,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125205935</v>
+        <v>125205942</v>
       </c>
       <c r="B17" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2303,21 +2293,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2327,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>784264</v>
+        <v>784340</v>
       </c>
       <c r="R17" t="n">
-        <v>7286244</v>
+        <v>7286230</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,10 +2379,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125205939</v>
+        <v>125205938</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
+        <v>96979</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2405,21 +2395,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2429,10 +2419,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>784306</v>
+        <v>784387</v>
       </c>
       <c r="R18" t="n">
-        <v>7286218</v>
+        <v>7286256</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2491,10 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125205937</v>
+        <v>125205948</v>
       </c>
       <c r="B19" t="n">
-        <v>96979</v>
+        <v>82597</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2503,25 +2493,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2531,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>784359</v>
+        <v>784378</v>
       </c>
       <c r="R19" t="n">
-        <v>7286440</v>
+        <v>7286451</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2593,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125205938</v>
+        <v>125205950</v>
       </c>
       <c r="B20" t="n">
-        <v>96979</v>
+        <v>82597</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2605,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2633,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>784387</v>
+        <v>784389</v>
       </c>
       <c r="R20" t="n">
-        <v>7286256</v>
+        <v>7286301</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,10 +2685,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125205961</v>
+        <v>125205945</v>
       </c>
       <c r="B21" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2707,25 +2697,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2735,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>784461</v>
+        <v>784321</v>
       </c>
       <c r="R21" t="n">
-        <v>7286446</v>
+        <v>7286252</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,10 +2787,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125201677</v>
+        <v>125205956</v>
       </c>
       <c r="B22" t="n">
-        <v>82597</v>
+        <v>56965</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,38 +2799,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>102954</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>784276</v>
+        <v>784280</v>
       </c>
       <c r="R22" t="n">
-        <v>7286135</v>
+        <v>7286150</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2870,9 +2868,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2887,22 +2895,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125205921</v>
+        <v>125201638</v>
       </c>
       <c r="B23" t="n">
-        <v>90977</v>
+        <v>78842</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2911,38 +2919,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>784282</v>
+        <v>784464</v>
       </c>
       <c r="R23" t="n">
-        <v>7286280</v>
+        <v>7286498</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2989,22 +2997,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125205932</v>
+        <v>125205949</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>82597</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3017,21 +3025,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3041,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>784380</v>
+        <v>784323</v>
       </c>
       <c r="R24" t="n">
-        <v>7286228</v>
+        <v>7286372</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3103,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125205925</v>
+        <v>125205932</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3119,16 +3127,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3136,33 +3144,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>784312</v>
+        <v>784380</v>
       </c>
       <c r="R25" t="n">
-        <v>7286305</v>
+        <v>7286228</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,19 +3184,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>17:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3231,10 +3213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125205949</v>
+        <v>125205944</v>
       </c>
       <c r="B26" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3247,21 +3229,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3274,7 +3256,7 @@
         <v>784323</v>
       </c>
       <c r="R26" t="n">
-        <v>7286372</v>
+        <v>7286284</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3333,10 +3315,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125205945</v>
+        <v>125205953</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>56965</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3345,38 +3327,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>102954</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>784321</v>
+        <v>784304</v>
       </c>
       <c r="R27" t="n">
-        <v>7286252</v>
+        <v>7286278</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,9 +3396,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3435,10 +3435,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125205959</v>
+        <v>125205941</v>
       </c>
       <c r="B28" t="n">
-        <v>96227</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3447,25 +3447,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2869</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>784478</v>
+        <v>784331</v>
       </c>
       <c r="R28" t="n">
-        <v>7286475</v>
+        <v>7286390</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125205948</v>
+        <v>125205958</v>
       </c>
       <c r="B29" t="n">
-        <v>82597</v>
+        <v>74893</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3553,21 +3553,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>784378</v>
+        <v>784424</v>
       </c>
       <c r="R29" t="n">
-        <v>7286451</v>
+        <v>7286482</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125205925</v>
+        <v>125205931</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,33 +708,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>784312</v>
+        <v>784313</v>
       </c>
       <c r="R2" t="n">
-        <v>7286305</v>
+        <v>7286297</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -776,7 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125201648</v>
+        <v>125205938</v>
       </c>
       <c r="B3" t="n">
-        <v>91457</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,38 +812,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784333</v>
+        <v>784387</v>
       </c>
       <c r="R3" t="n">
-        <v>7286210</v>
+        <v>7286256</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,11 +878,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gran bark kvar</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -898,22 +890,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125205943</v>
+        <v>125205956</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>56965</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,38 +914,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>102954</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784323</v>
+        <v>784280</v>
       </c>
       <c r="R4" t="n">
-        <v>7286243</v>
+        <v>7286150</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,9 +983,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125205939</v>
+        <v>125205935</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>91299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,25 +1034,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784306</v>
+        <v>784264</v>
       </c>
       <c r="R5" t="n">
-        <v>7286218</v>
+        <v>7286244</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125205921</v>
+        <v>125205952</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>82597</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,25 +1136,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784282</v>
+        <v>784330</v>
       </c>
       <c r="R6" t="n">
-        <v>7286280</v>
+        <v>7286266</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125205931</v>
+        <v>125205939</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,20 +1238,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1250,24 +1260,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784313</v>
+        <v>784306</v>
       </c>
       <c r="R7" t="n">
-        <v>7286297</v>
+        <v>7286218</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,24 +1299,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125205952</v>
+        <v>125205936</v>
       </c>
       <c r="B8" t="n">
-        <v>82597</v>
+        <v>96979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1340,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>784330</v>
+        <v>784312</v>
       </c>
       <c r="R8" t="n">
-        <v>7286266</v>
+        <v>7286355</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125205936</v>
+        <v>125205932</v>
       </c>
       <c r="B9" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1455,25 +1442,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>784312</v>
+        <v>784380</v>
       </c>
       <c r="R9" t="n">
-        <v>7286355</v>
+        <v>7286228</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125205937</v>
+        <v>125201648</v>
       </c>
       <c r="B10" t="n">
-        <v>96979</v>
+        <v>91457</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,38 +1544,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784359</v>
+        <v>784333</v>
       </c>
       <c r="R10" t="n">
-        <v>7286440</v>
+        <v>7286210</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,6 +1610,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gran bark kvar</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1635,22 +1627,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125201677</v>
+        <v>125205928</v>
       </c>
       <c r="B11" t="n">
-        <v>82597</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,34 +1655,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784276</v>
+        <v>784295</v>
       </c>
       <c r="R11" t="n">
-        <v>7286135</v>
+        <v>7286331</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,9 +1720,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1737,22 +1747,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125205928</v>
+        <v>125205961</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>96227</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,46 +1771,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784295</v>
+        <v>784461</v>
       </c>
       <c r="R12" t="n">
-        <v>7286331</v>
+        <v>7286446</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,19 +1832,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1869,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125205961</v>
+        <v>125205937</v>
       </c>
       <c r="B13" t="n">
-        <v>96227</v>
+        <v>96979</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1909,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>784461</v>
+        <v>784359</v>
       </c>
       <c r="R13" t="n">
-        <v>7286446</v>
+        <v>7286440</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125205935</v>
+        <v>125205943</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,21 +1979,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2011,10 +2003,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>784264</v>
+        <v>784323</v>
       </c>
       <c r="R14" t="n">
-        <v>7286244</v>
+        <v>7286243</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,10 +2065,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125205951</v>
+        <v>125205925</v>
       </c>
       <c r="B15" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2089,34 +2081,50 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>784382</v>
+        <v>784312</v>
       </c>
       <c r="R15" t="n">
-        <v>7286215</v>
+        <v>7286305</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,9 +2154,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2175,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125205959</v>
+        <v>125205953</v>
       </c>
       <c r="B16" t="n">
-        <v>96227</v>
+        <v>56965</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2191,34 +2209,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>102954</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>784478</v>
+        <v>784304</v>
       </c>
       <c r="R16" t="n">
-        <v>7286475</v>
+        <v>7286278</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,9 +2274,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2277,10 +2313,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125205942</v>
+        <v>125201638</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>78842</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2293,34 +2329,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>784340</v>
+        <v>784464</v>
       </c>
       <c r="R17" t="n">
-        <v>7286230</v>
+        <v>7286498</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,22 +2403,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125205938</v>
+        <v>125205949</v>
       </c>
       <c r="B18" t="n">
-        <v>96979</v>
+        <v>82597</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,25 +2427,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2419,10 +2455,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>784387</v>
+        <v>784323</v>
       </c>
       <c r="R18" t="n">
-        <v>7286256</v>
+        <v>7286372</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,10 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125205948</v>
+        <v>125205944</v>
       </c>
       <c r="B19" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2497,21 +2533,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2521,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>784378</v>
+        <v>784323</v>
       </c>
       <c r="R19" t="n">
-        <v>7286451</v>
+        <v>7286284</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125205950</v>
+        <v>125205958</v>
       </c>
       <c r="B20" t="n">
-        <v>82597</v>
+        <v>74893</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2635,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>784389</v>
+        <v>784424</v>
       </c>
       <c r="R20" t="n">
-        <v>7286301</v>
+        <v>7286482</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2685,10 +2721,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125205945</v>
+        <v>125205921</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2697,25 +2733,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2725,10 +2761,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>784321</v>
+        <v>784282</v>
       </c>
       <c r="R21" t="n">
-        <v>7286252</v>
+        <v>7286280</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2787,10 +2823,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125205956</v>
+        <v>125205941</v>
       </c>
       <c r="B22" t="n">
-        <v>56965</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,46 +2835,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102954</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>784280</v>
+        <v>784331</v>
       </c>
       <c r="R22" t="n">
-        <v>7286150</v>
+        <v>7286390</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2868,19 +2896,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2925,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125201638</v>
+        <v>125205951</v>
       </c>
       <c r="B23" t="n">
-        <v>78842</v>
+        <v>82597</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,34 +2941,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>784464</v>
+        <v>784382</v>
       </c>
       <c r="R23" t="n">
-        <v>7286498</v>
+        <v>7286215</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,22 +3015,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125205949</v>
+        <v>125205945</v>
       </c>
       <c r="B24" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3025,21 +3043,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3067,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>784323</v>
+        <v>784321</v>
       </c>
       <c r="R24" t="n">
-        <v>7286372</v>
+        <v>7286252</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,10 +3129,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125205932</v>
+        <v>125201677</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>82597</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3127,34 +3145,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>784380</v>
+        <v>784276</v>
       </c>
       <c r="R25" t="n">
-        <v>7286228</v>
+        <v>7286135</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,22 +3219,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125205944</v>
+        <v>125205942</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3229,21 +3247,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,10 +3271,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>784323</v>
+        <v>784340</v>
       </c>
       <c r="R26" t="n">
-        <v>7286284</v>
+        <v>7286230</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3315,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125205953</v>
+        <v>125205959</v>
       </c>
       <c r="B27" t="n">
-        <v>56965</v>
+        <v>96227</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3331,42 +3349,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102954</v>
+        <v>2869</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>784304</v>
+        <v>784478</v>
       </c>
       <c r="R27" t="n">
-        <v>7286278</v>
+        <v>7286475</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3396,19 +3406,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3435,10 +3435,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125205941</v>
+        <v>125205950</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3451,21 +3451,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>784331</v>
+        <v>784389</v>
       </c>
       <c r="R28" t="n">
-        <v>7286390</v>
+        <v>7286301</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125205958</v>
+        <v>125205948</v>
       </c>
       <c r="B29" t="n">
-        <v>74893</v>
+        <v>82597</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3553,21 +3553,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>784424</v>
+        <v>784378</v>
       </c>
       <c r="R29" t="n">
-        <v>7286482</v>
+        <v>7286451</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125205931</v>
+        <v>125205939</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,24 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>784313</v>
+        <v>784306</v>
       </c>
       <c r="R2" t="n">
-        <v>7286297</v>
+        <v>7286218</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,24 +748,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125205938</v>
+        <v>125205950</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>82597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784387</v>
+        <v>784389</v>
       </c>
       <c r="R3" t="n">
-        <v>7286256</v>
+        <v>7286301</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1022,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125205935</v>
+        <v>125205943</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784264</v>
+        <v>784323</v>
       </c>
       <c r="R5" t="n">
-        <v>7286244</v>
+        <v>7286243</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125205952</v>
+        <v>125205945</v>
       </c>
       <c r="B6" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784330</v>
+        <v>784321</v>
       </c>
       <c r="R6" t="n">
-        <v>7286266</v>
+        <v>7286252</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125205939</v>
+        <v>125205952</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>82597</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1266,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784306</v>
+        <v>784330</v>
       </c>
       <c r="R7" t="n">
-        <v>7286218</v>
+        <v>7286266</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125205936</v>
+        <v>125201638</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>78842</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,38 +1317,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>784312</v>
+        <v>784464</v>
       </c>
       <c r="R8" t="n">
-        <v>7286355</v>
+        <v>7286498</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,22 +1395,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125205932</v>
+        <v>125205958</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>74893</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1470,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>784380</v>
+        <v>784424</v>
       </c>
       <c r="R9" t="n">
-        <v>7286228</v>
+        <v>7286482</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125201648</v>
+        <v>125205942</v>
       </c>
       <c r="B10" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,38 +1521,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784333</v>
+        <v>784340</v>
       </c>
       <c r="R10" t="n">
-        <v>7286210</v>
+        <v>7286230</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,11 +1587,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gran bark kvar</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1627,22 +1599,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125205928</v>
+        <v>125205938</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>96979</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,46 +1623,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784295</v>
+        <v>784387</v>
       </c>
       <c r="R11" t="n">
-        <v>7286331</v>
+        <v>7286256</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,19 +1684,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125205961</v>
+        <v>125205925</v>
       </c>
       <c r="B12" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,38 +1725,54 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784461</v>
+        <v>784312</v>
       </c>
       <c r="R12" t="n">
-        <v>7286446</v>
+        <v>7286305</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,9 +1802,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,10 +1943,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125205943</v>
+        <v>125205932</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,21 +1959,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2003,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>784323</v>
+        <v>784380</v>
       </c>
       <c r="R14" t="n">
-        <v>7286243</v>
+        <v>7286228</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2065,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125205925</v>
+        <v>125205931</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,16 +2061,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2098,33 +2078,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>784312</v>
+        <v>784313</v>
       </c>
       <c r="R15" t="n">
-        <v>7286305</v>
+        <v>7286297</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2128,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2138,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2170,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125205953</v>
+        <v>125205961</v>
       </c>
       <c r="B16" t="n">
-        <v>56965</v>
+        <v>96227</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2209,42 +2186,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102954</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>784304</v>
+        <v>784461</v>
       </c>
       <c r="R16" t="n">
-        <v>7286278</v>
+        <v>7286446</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,19 +2243,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,10 +2272,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125201638</v>
+        <v>125205944</v>
       </c>
       <c r="B17" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2329,34 +2288,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>784464</v>
+        <v>784323</v>
       </c>
       <c r="R17" t="n">
-        <v>7286498</v>
+        <v>7286284</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,22 +2362,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125205949</v>
+        <v>125201648</v>
       </c>
       <c r="B18" t="n">
-        <v>82597</v>
+        <v>91457</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2427,38 +2386,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>784323</v>
+        <v>784333</v>
       </c>
       <c r="R18" t="n">
-        <v>7286372</v>
+        <v>7286210</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,6 +2452,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gran bark kvar</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2505,22 +2469,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125205944</v>
+        <v>125205941</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2533,21 +2497,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2557,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>784323</v>
+        <v>784331</v>
       </c>
       <c r="R19" t="n">
-        <v>7286284</v>
+        <v>7286390</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125205958</v>
+        <v>125205959</v>
       </c>
       <c r="B20" t="n">
-        <v>74893</v>
+        <v>96227</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>2869</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>784424</v>
+        <v>784478</v>
       </c>
       <c r="R20" t="n">
-        <v>7286482</v>
+        <v>7286475</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2721,10 +2685,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125205921</v>
+        <v>125205953</v>
       </c>
       <c r="B21" t="n">
-        <v>90977</v>
+        <v>56965</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2737,34 +2701,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>102954</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>784282</v>
+        <v>784304</v>
       </c>
       <c r="R21" t="n">
-        <v>7286280</v>
+        <v>7286278</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2794,9 +2766,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2823,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125205941</v>
+        <v>125205951</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2839,21 +2821,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2863,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>784331</v>
+        <v>784382</v>
       </c>
       <c r="R22" t="n">
-        <v>7286390</v>
+        <v>7286215</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125205951</v>
+        <v>125205928</v>
       </c>
       <c r="B23" t="n">
-        <v>82597</v>
+        <v>57666</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2941,34 +2923,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>784382</v>
+        <v>784295</v>
       </c>
       <c r="R23" t="n">
-        <v>7286215</v>
+        <v>7286331</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2998,9 +2988,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125205945</v>
+        <v>125205949</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>784321</v>
+        <v>784323</v>
       </c>
       <c r="R24" t="n">
-        <v>7286252</v>
+        <v>7286372</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3129,10 +3129,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125201677</v>
+        <v>125205936</v>
       </c>
       <c r="B25" t="n">
-        <v>82597</v>
+        <v>96979</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3141,38 +3141,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>784276</v>
+        <v>784312</v>
       </c>
       <c r="R25" t="n">
-        <v>7286135</v>
+        <v>7286355</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,22 +3219,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125205942</v>
+        <v>125201677</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3247,34 +3247,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>784340</v>
+        <v>784276</v>
       </c>
       <c r="R26" t="n">
-        <v>7286230</v>
+        <v>7286135</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3321,22 +3321,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125205959</v>
+        <v>125205921</v>
       </c>
       <c r="B27" t="n">
-        <v>96227</v>
+        <v>90977</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>784478</v>
+        <v>784282</v>
       </c>
       <c r="R27" t="n">
-        <v>7286475</v>
+        <v>7286280</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,10 +3435,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125205950</v>
+        <v>125205935</v>
       </c>
       <c r="B28" t="n">
-        <v>82597</v>
+        <v>91299</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3451,21 +3451,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>784389</v>
+        <v>784264</v>
       </c>
       <c r="R28" t="n">
-        <v>7286301</v>
+        <v>7286244</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3637,6 +3637,414 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125201671</v>
+      </c>
+      <c r="B30" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>784334</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7286197</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125201678</v>
+      </c>
+      <c r="B31" t="n">
+        <v>96227</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>784473</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7286440</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125201670</v>
+      </c>
+      <c r="B32" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>784308</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7286195</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125201679</v>
+      </c>
+      <c r="B33" t="n">
+        <v>96227</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>784366</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7286457</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125205950</v>
+        <v>125205956</v>
       </c>
       <c r="B3" t="n">
-        <v>82597</v>
+        <v>56965</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>102954</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784389</v>
+        <v>784280</v>
       </c>
       <c r="R3" t="n">
-        <v>7286301</v>
+        <v>7286150</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +858,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125205956</v>
+        <v>125205950</v>
       </c>
       <c r="B4" t="n">
-        <v>56965</v>
+        <v>82597</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,46 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102954</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784280</v>
+        <v>784389</v>
       </c>
       <c r="R4" t="n">
-        <v>7286150</v>
+        <v>7286301</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,19 +970,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2045,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125205931</v>
+        <v>125205961</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>96227</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,46 +2057,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>784313</v>
+        <v>784461</v>
       </c>
       <c r="R15" t="n">
-        <v>7286297</v>
+        <v>7286446</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,24 +2118,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2170,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125205961</v>
+        <v>125205931</v>
       </c>
       <c r="B16" t="n">
-        <v>96227</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2182,38 +2159,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>784461</v>
+        <v>784313</v>
       </c>
       <c r="R16" t="n">
-        <v>7286446</v>
+        <v>7286297</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,9 +2228,24 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -4045,6 +4045,2153 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125201641</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>784273</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7286260</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125201660</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>784394</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7286334</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125201656</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>784313</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7286267</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125201664</v>
+      </c>
+      <c r="B37" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>784378</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7286354</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125201666</v>
+      </c>
+      <c r="B38" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>784339</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7286244</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125201668</v>
+      </c>
+      <c r="B39" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>784327</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7286212</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125201650</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>658</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>784257</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7286240</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125201645</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>784360</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7286237</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125201663</v>
+      </c>
+      <c r="B42" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>784333</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7286405</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125201636</v>
+      </c>
+      <c r="B43" t="n">
+        <v>74901</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>784334</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7286242</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125201640</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>784265</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7286257</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125201642</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>784349</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7286343</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125201644</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>784368</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7286235</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125201646</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>784324</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7286201</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125201659</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>784312</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7286315</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125201639</v>
+      </c>
+      <c r="B49" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>784305</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7286333</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125201655</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>784464</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7286450</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125201661</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>784347</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7286236</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125201657</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>784313</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7286311</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125201635</v>
+      </c>
+      <c r="B53" t="n">
+        <v>74901</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>784271</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7286137</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På levande gran, +200, grå/vitt substrat,</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125201637</v>
+      </c>
+      <c r="B54" t="n">
+        <v>74901</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Långmyran- Strycktjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>784286</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7286144</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125205939</v>
+        <v>125205950</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>82597</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>784306</v>
+        <v>784389</v>
       </c>
       <c r="R2" t="n">
-        <v>7286218</v>
+        <v>7286301</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125205956</v>
+        <v>125205931</v>
       </c>
       <c r="B3" t="n">
-        <v>56965</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,20 +789,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -815,7 +815,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784280</v>
+        <v>784313</v>
       </c>
       <c r="R3" t="n">
-        <v>7286150</v>
+        <v>7286297</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125205950</v>
+        <v>125205951</v>
       </c>
       <c r="B4" t="n">
         <v>82597</v>
@@ -937,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784389</v>
+        <v>784382</v>
       </c>
       <c r="R4" t="n">
-        <v>7286301</v>
+        <v>7286215</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125205943</v>
+        <v>125201638</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>78842</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,34 +1020,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784323</v>
+        <v>784464</v>
       </c>
       <c r="R5" t="n">
-        <v>7286243</v>
+        <v>7286498</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,22 +1094,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125205945</v>
+        <v>125205938</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1118,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784321</v>
+        <v>784387</v>
       </c>
       <c r="R6" t="n">
-        <v>7286252</v>
+        <v>7286256</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1305,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125201638</v>
+        <v>125205935</v>
       </c>
       <c r="B8" t="n">
-        <v>78842</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,34 +1326,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>784464</v>
+        <v>784264</v>
       </c>
       <c r="R8" t="n">
-        <v>7286498</v>
+        <v>7286244</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,22 +1400,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125205958</v>
+        <v>125205928</v>
       </c>
       <c r="B9" t="n">
-        <v>74893</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,34 +1428,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>784424</v>
+        <v>784295</v>
       </c>
       <c r="R9" t="n">
-        <v>7286482</v>
+        <v>7286331</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,9 +1493,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,7 +1532,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125205942</v>
+        <v>125205941</v>
       </c>
       <c r="B10" t="n">
         <v>91030</v>
@@ -1549,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784340</v>
+        <v>784331</v>
       </c>
       <c r="R10" t="n">
-        <v>7286230</v>
+        <v>7286390</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125205938</v>
+        <v>125205943</v>
       </c>
       <c r="B11" t="n">
-        <v>96979</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784387</v>
+        <v>784323</v>
       </c>
       <c r="R11" t="n">
-        <v>7286256</v>
+        <v>7286243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125205925</v>
+        <v>125205953</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>56965</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,20 +1748,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>102954</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1746,11 +1769,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
@@ -1758,21 +1777,17 @@
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784312</v>
+        <v>784304</v>
       </c>
       <c r="R12" t="n">
-        <v>7286305</v>
+        <v>7286278</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,7 +1819,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1814,7 +1829,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125205937</v>
+        <v>125205949</v>
       </c>
       <c r="B13" t="n">
-        <v>96979</v>
+        <v>82597</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1868,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>784359</v>
+        <v>784323</v>
       </c>
       <c r="R13" t="n">
-        <v>7286440</v>
+        <v>7286372</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125205932</v>
+        <v>125205942</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,21 +1974,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,10 +1998,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>784380</v>
+        <v>784340</v>
       </c>
       <c r="R14" t="n">
-        <v>7286228</v>
+        <v>7286230</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125205961</v>
+        <v>125205944</v>
       </c>
       <c r="B15" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,25 +2072,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2085,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>784461</v>
+        <v>784323</v>
       </c>
       <c r="R15" t="n">
-        <v>7286446</v>
+        <v>7286284</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,10 +2162,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125205931</v>
+        <v>125205961</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>96227</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,46 +2174,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>784313</v>
+        <v>784461</v>
       </c>
       <c r="R16" t="n">
-        <v>7286297</v>
+        <v>7286446</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,24 +2235,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2272,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125205944</v>
+        <v>125205939</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2284,25 +2276,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2312,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>784323</v>
+        <v>784306</v>
       </c>
       <c r="R17" t="n">
-        <v>7286284</v>
+        <v>7286218</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2374,10 +2366,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125201648</v>
+        <v>125201677</v>
       </c>
       <c r="B18" t="n">
-        <v>91457</v>
+        <v>82597</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2386,25 +2378,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2414,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>784333</v>
+        <v>784276</v>
       </c>
       <c r="R18" t="n">
-        <v>7286210</v>
+        <v>7286135</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,11 +2442,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gran bark kvar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2481,10 +2468,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125205941</v>
+        <v>125205937</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>96979</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,25 +2480,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2521,10 +2508,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>784331</v>
+        <v>784359</v>
       </c>
       <c r="R19" t="n">
-        <v>7286390</v>
+        <v>7286440</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2570,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125205959</v>
+        <v>125205956</v>
       </c>
       <c r="B20" t="n">
-        <v>96227</v>
+        <v>56965</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,34 +2586,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>102954</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>784478</v>
+        <v>784280</v>
       </c>
       <c r="R20" t="n">
-        <v>7286475</v>
+        <v>7286150</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2656,9 +2651,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2685,10 +2690,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125205953</v>
+        <v>125205936</v>
       </c>
       <c r="B21" t="n">
-        <v>56965</v>
+        <v>96979</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,42 +2706,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102954</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>784304</v>
+        <v>784312</v>
       </c>
       <c r="R21" t="n">
-        <v>7286278</v>
+        <v>7286355</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2766,19 +2763,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2792,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125205951</v>
+        <v>125205948</v>
       </c>
       <c r="B22" t="n">
         <v>82597</v>
@@ -2845,10 +2832,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>784382</v>
+        <v>784378</v>
       </c>
       <c r="R22" t="n">
-        <v>7286215</v>
+        <v>7286451</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,10 +2894,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125205928</v>
+        <v>125205932</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,42 +2910,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>784295</v>
+        <v>784380</v>
       </c>
       <c r="R23" t="n">
-        <v>7286331</v>
+        <v>7286228</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,19 +2967,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,10 +2996,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125205949</v>
+        <v>125205958</v>
       </c>
       <c r="B24" t="n">
-        <v>82597</v>
+        <v>74893</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3043,21 +3012,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3067,10 +3036,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>784323</v>
+        <v>784424</v>
       </c>
       <c r="R24" t="n">
-        <v>7286372</v>
+        <v>7286482</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3129,10 +3098,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125205936</v>
+        <v>125205945</v>
       </c>
       <c r="B25" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3141,25 +3110,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3169,10 +3138,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>784312</v>
+        <v>784321</v>
       </c>
       <c r="R25" t="n">
-        <v>7286355</v>
+        <v>7286252</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,10 +3200,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125201677</v>
+        <v>125205959</v>
       </c>
       <c r="B26" t="n">
-        <v>82597</v>
+        <v>96227</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3243,38 +3212,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>784276</v>
+        <v>784478</v>
       </c>
       <c r="R26" t="n">
-        <v>7286135</v>
+        <v>7286475</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3321,12 +3290,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3435,10 +3404,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125205935</v>
+        <v>125205925</v>
       </c>
       <c r="B28" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3451,34 +3420,50 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>784264</v>
+        <v>784312</v>
       </c>
       <c r="R28" t="n">
-        <v>7286244</v>
+        <v>7286305</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3508,9 +3493,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3537,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125205948</v>
+        <v>125201648</v>
       </c>
       <c r="B29" t="n">
-        <v>82597</v>
+        <v>91457</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3549,38 +3544,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>784378</v>
+        <v>784333</v>
       </c>
       <c r="R29" t="n">
-        <v>7286451</v>
+        <v>7286210</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3615,6 +3610,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gran bark kvar</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3627,22 +3627,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125201671</v>
+        <v>125201678</v>
       </c>
       <c r="B30" t="n">
-        <v>82597</v>
+        <v>96227</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3651,25 +3651,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>784334</v>
+        <v>784473</v>
       </c>
       <c r="R30" t="n">
-        <v>7286197</v>
+        <v>7286440</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125201678</v>
+        <v>125201679</v>
       </c>
       <c r="B31" t="n">
         <v>96227</v>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>784473</v>
+        <v>784366</v>
       </c>
       <c r="R31" t="n">
-        <v>7286440</v>
+        <v>7286457</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125201670</v>
+        <v>125201671</v>
       </c>
       <c r="B32" t="n">
         <v>82597</v>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>784308</v>
+        <v>784334</v>
       </c>
       <c r="R32" t="n">
-        <v>7286195</v>
+        <v>7286197</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,10 +3945,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125201679</v>
+        <v>125201670</v>
       </c>
       <c r="B33" t="n">
-        <v>96227</v>
+        <v>82597</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3957,25 +3957,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>784366</v>
+        <v>784308</v>
       </c>
       <c r="R33" t="n">
-        <v>7286457</v>
+        <v>7286195</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125201660</v>
+        <v>125201663</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4165,21 +4165,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>784394</v>
+        <v>784333</v>
       </c>
       <c r="R35" t="n">
-        <v>7286334</v>
+        <v>7286405</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4251,10 +4251,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125201656</v>
+        <v>125201640</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>784313</v>
+        <v>784265</v>
       </c>
       <c r="R36" t="n">
-        <v>7286267</v>
+        <v>7286257</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4353,10 +4353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125201664</v>
+        <v>125201636</v>
       </c>
       <c r="B37" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4369,21 +4369,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>784378</v>
+        <v>784334</v>
       </c>
       <c r="R37" t="n">
-        <v>7286354</v>
+        <v>7286242</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125201666</v>
+        <v>125201655</v>
       </c>
       <c r="B38" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4467,25 +4467,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>784339</v>
+        <v>784464</v>
       </c>
       <c r="R38" t="n">
-        <v>7286244</v>
+        <v>7286450</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4557,7 +4557,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125201668</v>
+        <v>125201667</v>
       </c>
       <c r="B39" t="n">
         <v>82597</v>
@@ -4659,10 +4659,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125201650</v>
+        <v>125201660</v>
       </c>
       <c r="B40" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4675,21 +4675,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>784257</v>
+        <v>784394</v>
       </c>
       <c r="R40" t="n">
-        <v>7286240</v>
+        <v>7286334</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125201645</v>
+        <v>125201639</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4773,25 +4773,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>784360</v>
+        <v>784305</v>
       </c>
       <c r="R41" t="n">
-        <v>7286237</v>
+        <v>7286333</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125201663</v>
+        <v>125201659</v>
       </c>
       <c r="B42" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4879,21 +4879,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>784333</v>
+        <v>784312</v>
       </c>
       <c r="R42" t="n">
-        <v>7286405</v>
+        <v>7286315</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4965,10 +4965,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125201636</v>
+        <v>125201664</v>
       </c>
       <c r="B43" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4981,21 +4981,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>784334</v>
+        <v>784378</v>
       </c>
       <c r="R43" t="n">
-        <v>7286242</v>
+        <v>7286354</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5067,7 +5067,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125201640</v>
+        <v>125201645</v>
       </c>
       <c r="B44" t="n">
         <v>91012</v>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>784265</v>
+        <v>784360</v>
       </c>
       <c r="R44" t="n">
-        <v>7286257</v>
+        <v>7286237</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5169,7 +5169,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125201642</v>
+        <v>125201644</v>
       </c>
       <c r="B45" t="n">
         <v>91012</v>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>784349</v>
+        <v>784368</v>
       </c>
       <c r="R45" t="n">
-        <v>7286343</v>
+        <v>7286235</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5271,10 +5271,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125201644</v>
+        <v>125201666</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>82597</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>784368</v>
+        <v>784339</v>
       </c>
       <c r="R46" t="n">
-        <v>7286235</v>
+        <v>7286244</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125201646</v>
+        <v>125201650</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5389,21 +5389,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>784324</v>
+        <v>784257</v>
       </c>
       <c r="R47" t="n">
-        <v>7286201</v>
+        <v>7286240</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5475,10 +5475,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125201659</v>
+        <v>125201635</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5491,21 +5491,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5515,10 +5515,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>784312</v>
+        <v>784271</v>
       </c>
       <c r="R48" t="n">
-        <v>7286315</v>
+        <v>7286137</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5551,6 +5551,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På levande gran, +200, grå/vitt substrat,</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5577,10 +5582,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125201639</v>
+        <v>125201656</v>
       </c>
       <c r="B49" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5589,25 +5594,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5617,10 +5622,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>784305</v>
+        <v>784313</v>
       </c>
       <c r="R49" t="n">
-        <v>7286333</v>
+        <v>7286267</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5679,10 +5684,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125201655</v>
+        <v>125201661</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5691,25 +5696,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5719,10 +5724,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>784464</v>
+        <v>784347</v>
       </c>
       <c r="R50" t="n">
-        <v>7286450</v>
+        <v>7286236</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5781,10 +5786,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125201661</v>
+        <v>125201637</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5797,21 +5802,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5821,10 +5826,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>784347</v>
+        <v>784286</v>
       </c>
       <c r="R51" t="n">
-        <v>7286236</v>
+        <v>7286144</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5883,10 +5888,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125201657</v>
+        <v>125201646</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5899,21 +5904,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5923,10 +5928,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>784313</v>
+        <v>784324</v>
       </c>
       <c r="R52" t="n">
-        <v>7286311</v>
+        <v>7286201</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5985,10 +5990,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125201635</v>
+        <v>125201642</v>
       </c>
       <c r="B53" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6001,21 +6006,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6025,10 +6030,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>784271</v>
+        <v>784349</v>
       </c>
       <c r="R53" t="n">
-        <v>7286137</v>
+        <v>7286343</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6061,11 +6066,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På levande gran, +200, grå/vitt substrat,</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6092,10 +6092,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125201637</v>
+        <v>125201657</v>
       </c>
       <c r="B54" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6108,21 +6108,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6132,10 +6132,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>784286</v>
+        <v>784313</v>
       </c>
       <c r="R54" t="n">
-        <v>7286144</v>
+        <v>7286311</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125205951</v>
+        <v>125201638</v>
       </c>
       <c r="B4" t="n">
-        <v>82597</v>
+        <v>78842</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,34 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784382</v>
+        <v>784464</v>
       </c>
       <c r="R4" t="n">
-        <v>7286215</v>
+        <v>7286498</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,22 +992,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125201638</v>
+        <v>125205951</v>
       </c>
       <c r="B5" t="n">
-        <v>78842</v>
+        <v>82597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,34 +1020,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784464</v>
+        <v>784382</v>
       </c>
       <c r="R5" t="n">
-        <v>7286498</v>
+        <v>7286215</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,12 +1094,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125205931</v>
+        <v>125205925</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -810,25 +810,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784313</v>
+        <v>784312</v>
       </c>
       <c r="R3" t="n">
-        <v>7286297</v>
+        <v>7286305</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hackläte</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125201638</v>
+        <v>125205951</v>
       </c>
       <c r="B4" t="n">
-        <v>78842</v>
+        <v>82597</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,34 +921,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784464</v>
+        <v>784382</v>
       </c>
       <c r="R4" t="n">
-        <v>7286498</v>
+        <v>7286215</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,22 +995,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125205951</v>
+        <v>125205956</v>
       </c>
       <c r="B5" t="n">
-        <v>82597</v>
+        <v>56965</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,38 +1019,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784382</v>
+        <v>784280</v>
       </c>
       <c r="R5" t="n">
-        <v>7286215</v>
+        <v>7286150</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,9 +1088,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125205938</v>
+        <v>125205932</v>
       </c>
       <c r="B6" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,25 +1139,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784387</v>
+        <v>784380</v>
       </c>
       <c r="R6" t="n">
-        <v>7286256</v>
+        <v>7286228</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125205952</v>
+        <v>125205931</v>
       </c>
       <c r="B7" t="n">
-        <v>82597</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,34 +1245,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784330</v>
+        <v>784313</v>
       </c>
       <c r="R7" t="n">
-        <v>7286266</v>
+        <v>7286297</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,9 +1310,24 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125205935</v>
+        <v>125205928</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,34 +1370,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>784264</v>
+        <v>784295</v>
       </c>
       <c r="R8" t="n">
-        <v>7286244</v>
+        <v>7286331</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,9 +1435,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125205928</v>
+        <v>125205959</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>96227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,46 +1486,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>784295</v>
+        <v>784478</v>
       </c>
       <c r="R9" t="n">
-        <v>7286331</v>
+        <v>7286475</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,19 +1547,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125205941</v>
+        <v>125205953</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>56965</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,38 +1588,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>102954</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784331</v>
+        <v>784304</v>
       </c>
       <c r="R10" t="n">
-        <v>7286390</v>
+        <v>7286278</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1605,9 +1657,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125205943</v>
+        <v>125201648</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,38 +1708,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784323</v>
+        <v>784333</v>
       </c>
       <c r="R11" t="n">
-        <v>7286243</v>
+        <v>7286210</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,6 +1774,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gran bark kvar</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1724,22 +1791,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125205953</v>
+        <v>125205961</v>
       </c>
       <c r="B12" t="n">
-        <v>56965</v>
+        <v>96227</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,42 +1819,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102954</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784304</v>
+        <v>784461</v>
       </c>
       <c r="R12" t="n">
-        <v>7286278</v>
+        <v>7286446</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,19 +1876,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,10 +1905,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125205949</v>
+        <v>125205939</v>
       </c>
       <c r="B13" t="n">
-        <v>82597</v>
+        <v>57883</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,25 +1917,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1945,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>784323</v>
+        <v>784306</v>
       </c>
       <c r="R13" t="n">
-        <v>7286372</v>
+        <v>7286218</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125205942</v>
+        <v>125205937</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>96979</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,25 +2019,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1998,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>784340</v>
+        <v>784359</v>
       </c>
       <c r="R14" t="n">
-        <v>7286230</v>
+        <v>7286440</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,10 +2109,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125205944</v>
+        <v>125205938</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,25 +2121,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2100,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>784323</v>
+        <v>784387</v>
       </c>
       <c r="R15" t="n">
-        <v>7286284</v>
+        <v>7286256</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,10 +2211,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125205961</v>
+        <v>125205936</v>
       </c>
       <c r="B16" t="n">
-        <v>96227</v>
+        <v>96979</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2178,21 +2227,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2202,10 +2251,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>784461</v>
+        <v>784312</v>
       </c>
       <c r="R16" t="n">
-        <v>7286446</v>
+        <v>7286355</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2264,10 +2313,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125205939</v>
+        <v>125205952</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>82597</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,25 +2325,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2304,10 +2353,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>784306</v>
+        <v>784330</v>
       </c>
       <c r="R17" t="n">
-        <v>7286218</v>
+        <v>7286266</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125201677</v>
+        <v>125205921</v>
       </c>
       <c r="B18" t="n">
-        <v>82597</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2378,38 +2427,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>784276</v>
+        <v>784282</v>
       </c>
       <c r="R18" t="n">
-        <v>7286135</v>
+        <v>7286280</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2456,22 +2505,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125205937</v>
+        <v>125205949</v>
       </c>
       <c r="B19" t="n">
-        <v>96979</v>
+        <v>82597</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,25 +2529,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2508,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>784359</v>
+        <v>784323</v>
       </c>
       <c r="R19" t="n">
-        <v>7286440</v>
+        <v>7286372</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2570,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125205956</v>
+        <v>125205941</v>
       </c>
       <c r="B20" t="n">
-        <v>56965</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2582,46 +2631,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102954</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>784280</v>
+        <v>784331</v>
       </c>
       <c r="R20" t="n">
-        <v>7286150</v>
+        <v>7286390</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,19 +2692,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2690,10 +2721,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125205936</v>
+        <v>125205944</v>
       </c>
       <c r="B21" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2702,25 +2733,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2730,10 +2761,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>784312</v>
+        <v>784323</v>
       </c>
       <c r="R21" t="n">
-        <v>7286355</v>
+        <v>7286284</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2792,10 +2823,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125205948</v>
+        <v>125205943</v>
       </c>
       <c r="B22" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2808,21 +2839,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2832,10 +2863,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>784378</v>
+        <v>784323</v>
       </c>
       <c r="R22" t="n">
-        <v>7286451</v>
+        <v>7286243</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,10 +2925,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125205932</v>
+        <v>125205948</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>82597</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2910,21 +2941,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2934,10 +2965,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>784380</v>
+        <v>784378</v>
       </c>
       <c r="R23" t="n">
-        <v>7286228</v>
+        <v>7286451</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125205958</v>
+        <v>125201638</v>
       </c>
       <c r="B24" t="n">
-        <v>74893</v>
+        <v>78842</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3012,34 +3043,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>784424</v>
+        <v>784464</v>
       </c>
       <c r="R24" t="n">
-        <v>7286482</v>
+        <v>7286498</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3086,22 +3117,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125205945</v>
+        <v>125205942</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3114,21 +3145,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3138,10 +3169,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>784321</v>
+        <v>784340</v>
       </c>
       <c r="R25" t="n">
-        <v>7286252</v>
+        <v>7286230</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3200,10 +3231,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125205959</v>
+        <v>125205945</v>
       </c>
       <c r="B26" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3212,25 +3243,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3240,10 +3271,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>784478</v>
+        <v>784321</v>
       </c>
       <c r="R26" t="n">
-        <v>7286475</v>
+        <v>7286252</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3302,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125205921</v>
+        <v>125201677</v>
       </c>
       <c r="B27" t="n">
-        <v>90977</v>
+        <v>82597</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3314,38 +3345,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>784282</v>
+        <v>784276</v>
       </c>
       <c r="R27" t="n">
-        <v>7286280</v>
+        <v>7286135</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3392,22 +3423,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125205925</v>
+        <v>125205935</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3420,50 +3451,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>784312</v>
+        <v>784264</v>
       </c>
       <c r="R28" t="n">
-        <v>7286305</v>
+        <v>7286244</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3493,19 +3508,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125201648</v>
+        <v>125205958</v>
       </c>
       <c r="B29" t="n">
-        <v>91457</v>
+        <v>74893</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3544,38 +3549,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>784333</v>
+        <v>784424</v>
       </c>
       <c r="R29" t="n">
-        <v>7286210</v>
+        <v>7286482</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3610,11 +3615,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gran bark kvar</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3627,12 +3627,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125201679</v>
+        <v>125201670</v>
       </c>
       <c r="B31" t="n">
-        <v>96227</v>
+        <v>82597</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3753,25 +3753,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>784366</v>
+        <v>784308</v>
       </c>
       <c r="R31" t="n">
-        <v>7286457</v>
+        <v>7286195</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3945,10 +3945,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125201670</v>
+        <v>125201679</v>
       </c>
       <c r="B33" t="n">
-        <v>82597</v>
+        <v>96227</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3957,25 +3957,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>784308</v>
+        <v>784366</v>
       </c>
       <c r="R33" t="n">
-        <v>7286195</v>
+        <v>7286457</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125201641</v>
+        <v>125201642</v>
       </c>
       <c r="B34" t="n">
         <v>91012</v>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>784273</v>
+        <v>784349</v>
       </c>
       <c r="R34" t="n">
-        <v>7286260</v>
+        <v>7286343</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125201663</v>
+        <v>125201646</v>
       </c>
       <c r="B35" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4165,21 +4165,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>784333</v>
+        <v>784324</v>
       </c>
       <c r="R35" t="n">
-        <v>7286405</v>
+        <v>7286201</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4251,10 +4251,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125201640</v>
+        <v>125201635</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>784265</v>
+        <v>784271</v>
       </c>
       <c r="R36" t="n">
-        <v>7286257</v>
+        <v>7286137</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4327,6 +4327,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På levande gran, +200, grå/vitt substrat,</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4353,10 +4358,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125201636</v>
+        <v>125201655</v>
       </c>
       <c r="B37" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4365,25 +4370,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4393,10 +4398,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>784334</v>
+        <v>784464</v>
       </c>
       <c r="R37" t="n">
-        <v>7286242</v>
+        <v>7286450</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4455,10 +4460,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125201655</v>
+        <v>125201666</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4467,25 +4472,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4495,10 +4500,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>784464</v>
+        <v>784339</v>
       </c>
       <c r="R38" t="n">
-        <v>7286450</v>
+        <v>7286244</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4557,10 +4562,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125201667</v>
+        <v>125201661</v>
       </c>
       <c r="B39" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4573,21 +4578,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4597,10 +4602,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>784327</v>
+        <v>784347</v>
       </c>
       <c r="R39" t="n">
-        <v>7286212</v>
+        <v>7286236</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4659,10 +4664,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125201660</v>
+        <v>125201641</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4675,21 +4680,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4699,10 +4704,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>784394</v>
+        <v>784273</v>
       </c>
       <c r="R40" t="n">
-        <v>7286334</v>
+        <v>7286260</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4761,10 +4766,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125201639</v>
+        <v>125201667</v>
       </c>
       <c r="B41" t="n">
-        <v>90977</v>
+        <v>82597</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4773,25 +4778,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4801,10 +4806,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>784305</v>
+        <v>784327</v>
       </c>
       <c r="R41" t="n">
-        <v>7286333</v>
+        <v>7286212</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4863,10 +4868,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125201659</v>
+        <v>125201636</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4879,21 +4884,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4903,10 +4908,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>784312</v>
+        <v>784334</v>
       </c>
       <c r="R42" t="n">
-        <v>7286315</v>
+        <v>7286242</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4965,10 +4970,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125201664</v>
+        <v>125201639</v>
       </c>
       <c r="B43" t="n">
-        <v>82597</v>
+        <v>90977</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4977,25 +4982,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5005,10 +5010,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>784378</v>
+        <v>784305</v>
       </c>
       <c r="R43" t="n">
-        <v>7286354</v>
+        <v>7286333</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5067,7 +5072,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125201645</v>
+        <v>125201644</v>
       </c>
       <c r="B44" t="n">
         <v>91012</v>
@@ -5107,10 +5112,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>784360</v>
+        <v>784368</v>
       </c>
       <c r="R44" t="n">
-        <v>7286237</v>
+        <v>7286235</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5169,10 +5174,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125201644</v>
+        <v>125201637</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5185,21 +5190,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5209,10 +5214,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>784368</v>
+        <v>784286</v>
       </c>
       <c r="R45" t="n">
-        <v>7286235</v>
+        <v>7286144</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5271,10 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125201666</v>
+        <v>125201650</v>
       </c>
       <c r="B46" t="n">
-        <v>82597</v>
+        <v>91299</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5287,21 +5292,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5311,10 +5316,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>784339</v>
+        <v>784257</v>
       </c>
       <c r="R46" t="n">
-        <v>7286244</v>
+        <v>7286240</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5373,10 +5378,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125201650</v>
+        <v>125201663</v>
       </c>
       <c r="B47" t="n">
-        <v>91299</v>
+        <v>82597</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5389,21 +5394,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5413,10 +5418,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>784257</v>
+        <v>784333</v>
       </c>
       <c r="R47" t="n">
-        <v>7286240</v>
+        <v>7286405</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5475,10 +5480,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125201635</v>
+        <v>125201659</v>
       </c>
       <c r="B48" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5491,21 +5496,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5515,10 +5520,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>784271</v>
+        <v>784312</v>
       </c>
       <c r="R48" t="n">
-        <v>7286137</v>
+        <v>7286315</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5551,11 +5556,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På levande gran, +200, grå/vitt substrat,</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5582,10 +5582,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125201656</v>
+        <v>125201645</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5598,21 +5598,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>784313</v>
+        <v>784360</v>
       </c>
       <c r="R49" t="n">
-        <v>7286267</v>
+        <v>7286237</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5684,10 +5684,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125201661</v>
+        <v>125201664</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5700,21 +5700,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>784347</v>
+        <v>784378</v>
       </c>
       <c r="R50" t="n">
-        <v>7286236</v>
+        <v>7286354</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5786,10 +5786,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125201637</v>
+        <v>125201660</v>
       </c>
       <c r="B51" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5802,21 +5802,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5826,10 +5826,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>784286</v>
+        <v>784394</v>
       </c>
       <c r="R51" t="n">
-        <v>7286144</v>
+        <v>7286334</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5888,10 +5888,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125201646</v>
+        <v>125201656</v>
       </c>
       <c r="B52" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5904,21 +5904,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>784324</v>
+        <v>784313</v>
       </c>
       <c r="R52" t="n">
-        <v>7286201</v>
+        <v>7286267</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125201642</v>
+        <v>125201657</v>
       </c>
       <c r="B53" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>784349</v>
+        <v>784313</v>
       </c>
       <c r="R53" t="n">
-        <v>7286343</v>
+        <v>7286311</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6092,10 +6092,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125201657</v>
+        <v>125201640</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6108,21 +6108,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6132,10 +6132,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>784313</v>
+        <v>784265</v>
       </c>
       <c r="R54" t="n">
-        <v>7286311</v>
+        <v>7286257</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125205950</v>
+        <v>125205939</v>
       </c>
       <c r="B2" t="n">
-        <v>82597</v>
+        <v>58001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>784389</v>
+        <v>784306</v>
       </c>
       <c r="R2" t="n">
-        <v>7286301</v>
+        <v>7286218</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125205925</v>
+        <v>125205941</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,50 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784312</v>
+        <v>784331</v>
       </c>
       <c r="R3" t="n">
-        <v>7286305</v>
+        <v>7286390</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,19 +850,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125205951</v>
+        <v>125205945</v>
       </c>
       <c r="B4" t="n">
-        <v>82597</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784382</v>
+        <v>784321</v>
       </c>
       <c r="R4" t="n">
-        <v>7286215</v>
+        <v>7286252</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125205956</v>
+        <v>125205951</v>
       </c>
       <c r="B5" t="n">
-        <v>56965</v>
+        <v>82737</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,46 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784280</v>
+        <v>784382</v>
       </c>
       <c r="R5" t="n">
-        <v>7286150</v>
+        <v>7286215</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,19 +1054,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125205932</v>
+        <v>125205925</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,16 +1099,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1160,17 +1116,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784380</v>
+        <v>784312</v>
       </c>
       <c r="R6" t="n">
-        <v>7286228</v>
+        <v>7286305</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,9 +1172,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125205931</v>
+        <v>125205950</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>82737</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,42 +1227,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784313</v>
+        <v>784389</v>
       </c>
       <c r="R7" t="n">
-        <v>7286297</v>
+        <v>7286301</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,24 +1284,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125205928</v>
+        <v>125205931</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57632</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,21 +1329,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,7 +1351,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1402,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>784295</v>
+        <v>784313</v>
       </c>
       <c r="R8" t="n">
-        <v>7286331</v>
+        <v>7286297</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1396,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1406,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125205959</v>
+        <v>125205938</v>
       </c>
       <c r="B9" t="n">
-        <v>96227</v>
+        <v>97147</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>784478</v>
+        <v>784387</v>
       </c>
       <c r="R9" t="n">
-        <v>7286475</v>
+        <v>7286256</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125205953</v>
+        <v>125205932</v>
       </c>
       <c r="B10" t="n">
-        <v>56965</v>
+        <v>57632</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,20 +1552,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102954</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1610,24 +1574,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784304</v>
+        <v>784380</v>
       </c>
       <c r="R10" t="n">
-        <v>7286278</v>
+        <v>7286228</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1657,19 +1613,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125201648</v>
+        <v>125205937</v>
       </c>
       <c r="B11" t="n">
-        <v>91457</v>
+        <v>97147</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,38 +1654,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784333</v>
+        <v>784359</v>
       </c>
       <c r="R11" t="n">
-        <v>7286210</v>
+        <v>7286440</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1774,11 +1720,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gran bark kvar</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1791,22 +1732,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125205961</v>
+        <v>125205952</v>
       </c>
       <c r="B12" t="n">
-        <v>96227</v>
+        <v>82737</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1815,25 +1756,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1843,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784461</v>
+        <v>784330</v>
       </c>
       <c r="R12" t="n">
-        <v>7286446</v>
+        <v>7286266</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125205939</v>
+        <v>125201648</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>91617</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1917,38 +1858,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>784306</v>
+        <v>784333</v>
       </c>
       <c r="R13" t="n">
-        <v>7286218</v>
+        <v>7286210</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,6 +1924,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gran bark kvar</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1995,22 +1941,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125205937</v>
+        <v>125201638</v>
       </c>
       <c r="B14" t="n">
-        <v>96979</v>
+        <v>78979</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,38 +1965,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>784359</v>
+        <v>784464</v>
       </c>
       <c r="R14" t="n">
-        <v>7286440</v>
+        <v>7286498</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,22 +2043,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125205938</v>
+        <v>125205953</v>
       </c>
       <c r="B15" t="n">
-        <v>96979</v>
+        <v>57053</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2125,34 +2071,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>102954</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>784387</v>
+        <v>784304</v>
       </c>
       <c r="R15" t="n">
-        <v>7286256</v>
+        <v>7286278</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2182,9 +2136,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2211,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125205936</v>
+        <v>125205958</v>
       </c>
       <c r="B16" t="n">
-        <v>96979</v>
+        <v>75017</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2223,25 +2187,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2251,10 +2215,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>784312</v>
+        <v>784424</v>
       </c>
       <c r="R16" t="n">
-        <v>7286355</v>
+        <v>7286482</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125205952</v>
+        <v>125205961</v>
       </c>
       <c r="B17" t="n">
-        <v>82597</v>
+        <v>96395</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2325,25 +2289,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2353,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>784330</v>
+        <v>784461</v>
       </c>
       <c r="R17" t="n">
-        <v>7286266</v>
+        <v>7286446</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,10 +2379,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125205921</v>
+        <v>125205959</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>96395</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2431,21 +2395,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2455,10 +2419,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>784282</v>
+        <v>784478</v>
       </c>
       <c r="R18" t="n">
-        <v>7286280</v>
+        <v>7286475</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,10 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125205949</v>
+        <v>125205935</v>
       </c>
       <c r="B19" t="n">
-        <v>82597</v>
+        <v>91459</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2533,21 +2497,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2557,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>784323</v>
+        <v>784264</v>
       </c>
       <c r="R19" t="n">
-        <v>7286372</v>
+        <v>7286244</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125205941</v>
+        <v>125205928</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>57793</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2635,34 +2599,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>784331</v>
+        <v>784295</v>
       </c>
       <c r="R20" t="n">
-        <v>7286390</v>
+        <v>7286331</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,9 +2664,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2721,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125205944</v>
+        <v>125205942</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91184</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2737,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2761,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>784323</v>
+        <v>784340</v>
       </c>
       <c r="R21" t="n">
-        <v>7286284</v>
+        <v>7286230</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125205943</v>
+        <v>125205944</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>78947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2839,21 +2821,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2866,7 +2848,7 @@
         <v>784323</v>
       </c>
       <c r="R22" t="n">
-        <v>7286243</v>
+        <v>7286284</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125205948</v>
+        <v>125201677</v>
       </c>
       <c r="B23" t="n">
-        <v>82597</v>
+        <v>82737</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2961,14 +2943,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>784378</v>
+        <v>784276</v>
       </c>
       <c r="R23" t="n">
-        <v>7286451</v>
+        <v>7286135</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,22 +2997,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125201638</v>
+        <v>125205921</v>
       </c>
       <c r="B24" t="n">
-        <v>78842</v>
+        <v>91131</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3039,38 +3021,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>784464</v>
+        <v>784282</v>
       </c>
       <c r="R24" t="n">
-        <v>7286498</v>
+        <v>7286280</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3117,22 +3099,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125205942</v>
+        <v>125205956</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>57053</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3141,38 +3123,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>102954</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>784340</v>
+        <v>784280</v>
       </c>
       <c r="R25" t="n">
-        <v>7286230</v>
+        <v>7286150</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,9 +3192,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3231,10 +3231,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125205945</v>
+        <v>125205936</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>97147</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3243,25 +3243,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>784321</v>
+        <v>784312</v>
       </c>
       <c r="R26" t="n">
-        <v>7286252</v>
+        <v>7286355</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125201677</v>
+        <v>125205943</v>
       </c>
       <c r="B27" t="n">
-        <v>82597</v>
+        <v>91184</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3349,34 +3349,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>784276</v>
+        <v>784323</v>
       </c>
       <c r="R27" t="n">
-        <v>7286135</v>
+        <v>7286243</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3423,22 +3423,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125205935</v>
+        <v>125205948</v>
       </c>
       <c r="B28" t="n">
-        <v>91299</v>
+        <v>82737</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3451,21 +3451,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>784264</v>
+        <v>784378</v>
       </c>
       <c r="R28" t="n">
-        <v>7286244</v>
+        <v>7286451</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125205958</v>
+        <v>125205949</v>
       </c>
       <c r="B29" t="n">
-        <v>74893</v>
+        <v>82737</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3553,21 +3553,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>784424</v>
+        <v>784323</v>
       </c>
       <c r="R29" t="n">
-        <v>7286482</v>
+        <v>7286372</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,10 +3639,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125201678</v>
+        <v>125201671</v>
       </c>
       <c r="B30" t="n">
-        <v>96227</v>
+        <v>82737</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3651,25 +3651,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>784473</v>
+        <v>784334</v>
       </c>
       <c r="R30" t="n">
-        <v>7286440</v>
+        <v>7286197</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125201670</v>
+        <v>125201678</v>
       </c>
       <c r="B31" t="n">
-        <v>82597</v>
+        <v>96395</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3753,25 +3753,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>784308</v>
+        <v>784473</v>
       </c>
       <c r="R31" t="n">
-        <v>7286195</v>
+        <v>7286440</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,10 +3843,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125201671</v>
+        <v>125201679</v>
       </c>
       <c r="B32" t="n">
-        <v>82597</v>
+        <v>96395</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3855,25 +3855,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>784334</v>
+        <v>784366</v>
       </c>
       <c r="R32" t="n">
-        <v>7286197</v>
+        <v>7286457</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,10 +3945,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125201679</v>
+        <v>125201670</v>
       </c>
       <c r="B33" t="n">
-        <v>96227</v>
+        <v>82737</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3957,25 +3957,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>784366</v>
+        <v>784308</v>
       </c>
       <c r="R33" t="n">
-        <v>7286457</v>
+        <v>7286195</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4047,10 +4047,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125201642</v>
+        <v>125201635</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>75025</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>784349</v>
+        <v>784271</v>
       </c>
       <c r="R34" t="n">
-        <v>7286343</v>
+        <v>7286137</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4123,6 +4123,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På levande gran, +200, grå/vitt substrat,</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4149,10 +4154,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125201646</v>
+        <v>125201657</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4165,21 +4170,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4189,10 +4194,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>784324</v>
+        <v>784313</v>
       </c>
       <c r="R35" t="n">
-        <v>7286201</v>
+        <v>7286311</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4251,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125201635</v>
+        <v>125201641</v>
       </c>
       <c r="B36" t="n">
-        <v>74901</v>
+        <v>91166</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4267,21 +4272,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4291,10 +4296,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>784271</v>
+        <v>784273</v>
       </c>
       <c r="R36" t="n">
-        <v>7286137</v>
+        <v>7286260</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4327,11 +4332,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På levande gran, +200, grå/vitt substrat,</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4358,10 +4358,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125201655</v>
+        <v>125201645</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4370,25 +4370,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>784464</v>
+        <v>784360</v>
       </c>
       <c r="R37" t="n">
-        <v>7286450</v>
+        <v>7286237</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4460,10 +4460,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125201666</v>
+        <v>125201646</v>
       </c>
       <c r="B38" t="n">
-        <v>82597</v>
+        <v>91166</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4476,21 +4476,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>784339</v>
+        <v>784324</v>
       </c>
       <c r="R38" t="n">
-        <v>7286244</v>
+        <v>7286201</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4562,10 +4562,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125201661</v>
+        <v>125201666</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>82737</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4578,21 +4578,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>784347</v>
+        <v>784339</v>
       </c>
       <c r="R39" t="n">
-        <v>7286236</v>
+        <v>7286244</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125201641</v>
+        <v>125201659</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4680,21 +4680,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>784273</v>
+        <v>784312</v>
       </c>
       <c r="R40" t="n">
-        <v>7286260</v>
+        <v>7286315</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125201667</v>
+        <v>125201636</v>
       </c>
       <c r="B41" t="n">
-        <v>82597</v>
+        <v>75025</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4782,21 +4782,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>784327</v>
+        <v>784334</v>
       </c>
       <c r="R41" t="n">
-        <v>7286212</v>
+        <v>7286242</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125201636</v>
+        <v>125201644</v>
       </c>
       <c r="B42" t="n">
-        <v>74901</v>
+        <v>91166</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>784334</v>
+        <v>784368</v>
       </c>
       <c r="R42" t="n">
-        <v>7286242</v>
+        <v>7286235</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4970,10 +4970,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125201639</v>
+        <v>125201664</v>
       </c>
       <c r="B43" t="n">
-        <v>90977</v>
+        <v>82737</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4982,25 +4982,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>784305</v>
+        <v>784378</v>
       </c>
       <c r="R43" t="n">
-        <v>7286333</v>
+        <v>7286354</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125201644</v>
+        <v>125201661</v>
       </c>
       <c r="B44" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5088,21 +5088,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5112,10 +5112,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>784368</v>
+        <v>784347</v>
       </c>
       <c r="R44" t="n">
-        <v>7286235</v>
+        <v>7286236</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5174,10 +5174,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125201637</v>
+        <v>125201655</v>
       </c>
       <c r="B45" t="n">
-        <v>74901</v>
+        <v>98269</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5186,25 +5186,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5214,10 +5214,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>784286</v>
+        <v>784464</v>
       </c>
       <c r="R45" t="n">
-        <v>7286144</v>
+        <v>7286450</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5276,10 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125201650</v>
+        <v>125201668</v>
       </c>
       <c r="B46" t="n">
-        <v>91299</v>
+        <v>82737</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5292,21 +5292,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5316,10 +5316,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>784257</v>
+        <v>784327</v>
       </c>
       <c r="R46" t="n">
-        <v>7286240</v>
+        <v>7286212</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5378,10 +5378,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125201663</v>
+        <v>125201642</v>
       </c>
       <c r="B47" t="n">
-        <v>82597</v>
+        <v>91166</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>784333</v>
+        <v>784349</v>
       </c>
       <c r="R47" t="n">
-        <v>7286405</v>
+        <v>7286343</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5480,10 +5480,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125201659</v>
+        <v>125201640</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5496,21 +5496,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>784312</v>
+        <v>784265</v>
       </c>
       <c r="R48" t="n">
-        <v>7286315</v>
+        <v>7286257</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5582,10 +5582,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125201645</v>
+        <v>125201639</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>91131</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5594,25 +5594,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>784360</v>
+        <v>784305</v>
       </c>
       <c r="R49" t="n">
-        <v>7286237</v>
+        <v>7286333</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5684,10 +5684,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125201664</v>
+        <v>125201650</v>
       </c>
       <c r="B50" t="n">
-        <v>82597</v>
+        <v>91459</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5700,21 +5700,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>784378</v>
+        <v>784257</v>
       </c>
       <c r="R50" t="n">
-        <v>7286354</v>
+        <v>7286240</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5789,7 +5789,7 @@
         <v>125201660</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5888,10 +5888,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125201656</v>
+        <v>125201637</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>75025</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5904,21 +5904,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>784313</v>
+        <v>784286</v>
       </c>
       <c r="R52" t="n">
-        <v>7286267</v>
+        <v>7286144</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125201657</v>
+        <v>125201656</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>784313</v>
       </c>
       <c r="R53" t="n">
-        <v>7286311</v>
+        <v>7286267</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6092,10 +6092,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125201640</v>
+        <v>125201663</v>
       </c>
       <c r="B54" t="n">
-        <v>91012</v>
+        <v>82737</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6108,21 +6108,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6132,10 +6132,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>784265</v>
+        <v>784333</v>
       </c>
       <c r="R54" t="n">
-        <v>7286257</v>
+        <v>7286405</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125205945</v>
+        <v>125205951</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>82737</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784321</v>
+        <v>784382</v>
       </c>
       <c r="R4" t="n">
-        <v>7286252</v>
+        <v>7286215</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125205951</v>
+        <v>125205945</v>
       </c>
       <c r="B5" t="n">
-        <v>82737</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784382</v>
+        <v>784321</v>
       </c>
       <c r="R5" t="n">
-        <v>7286215</v>
+        <v>7286252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125205925</v>
+        <v>125205931</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,16 +1099,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1116,33 +1116,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784312</v>
+        <v>784313</v>
       </c>
       <c r="R6" t="n">
-        <v>7286305</v>
+        <v>7286297</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,7 +1166,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1184,7 +1176,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125205950</v>
+        <v>125205925</v>
       </c>
       <c r="B7" t="n">
-        <v>82737</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,34 +1224,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784389</v>
+        <v>784312</v>
       </c>
       <c r="R7" t="n">
-        <v>7286301</v>
+        <v>7286305</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,9 +1297,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125205931</v>
+        <v>125205950</v>
       </c>
       <c r="B8" t="n">
-        <v>57632</v>
+        <v>82737</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,42 +1352,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>784313</v>
+        <v>784389</v>
       </c>
       <c r="R8" t="n">
-        <v>7286297</v>
+        <v>7286301</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,24 +1409,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -5480,10 +5480,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125201640</v>
+        <v>125201639</v>
       </c>
       <c r="B48" t="n">
-        <v>91166</v>
+        <v>91131</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5492,25 +5492,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>784265</v>
+        <v>784305</v>
       </c>
       <c r="R48" t="n">
-        <v>7286257</v>
+        <v>7286333</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5582,10 +5582,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125201639</v>
+        <v>125201640</v>
       </c>
       <c r="B49" t="n">
-        <v>91131</v>
+        <v>91166</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5594,25 +5594,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>784305</v>
+        <v>784265</v>
       </c>
       <c r="R49" t="n">
-        <v>7286333</v>
+        <v>7286257</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125205939</v>
+        <v>125205950</v>
       </c>
       <c r="B2" t="n">
-        <v>58001</v>
+        <v>82737</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>784306</v>
+        <v>784389</v>
       </c>
       <c r="R2" t="n">
-        <v>7286218</v>
+        <v>7286301</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125205941</v>
+        <v>125205945</v>
       </c>
       <c r="B3" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784331</v>
+        <v>784321</v>
       </c>
       <c r="R3" t="n">
-        <v>7286390</v>
+        <v>7286252</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125205951</v>
+        <v>125205959</v>
       </c>
       <c r="B4" t="n">
-        <v>82737</v>
+        <v>96395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784382</v>
+        <v>784478</v>
       </c>
       <c r="R4" t="n">
-        <v>7286215</v>
+        <v>7286475</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125205945</v>
+        <v>125205948</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
+        <v>82737</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784321</v>
+        <v>784378</v>
       </c>
       <c r="R5" t="n">
-        <v>7286252</v>
+        <v>7286451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125205931</v>
+        <v>125205939</v>
       </c>
       <c r="B6" t="n">
-        <v>57632</v>
+        <v>58001</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,20 +1095,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1117,24 +1117,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784313</v>
+        <v>784306</v>
       </c>
       <c r="R6" t="n">
-        <v>7286297</v>
+        <v>7286218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,24 +1156,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125205925</v>
+        <v>125205956</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
+        <v>57053</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,20 +1197,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>102954</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1241,11 +1218,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
@@ -1253,21 +1226,17 @@
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784312</v>
+        <v>784280</v>
       </c>
       <c r="R7" t="n">
-        <v>7286305</v>
+        <v>7286150</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1268,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1278,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125205950</v>
+        <v>125205921</v>
       </c>
       <c r="B8" t="n">
-        <v>82737</v>
+        <v>91131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,25 +1317,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>784389</v>
+        <v>784282</v>
       </c>
       <c r="R8" t="n">
-        <v>7286301</v>
+        <v>7286280</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125205938</v>
+        <v>125205952</v>
       </c>
       <c r="B9" t="n">
-        <v>97147</v>
+        <v>82737</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>784387</v>
+        <v>784330</v>
       </c>
       <c r="R9" t="n">
-        <v>7286256</v>
+        <v>7286266</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125205932</v>
+        <v>125205942</v>
       </c>
       <c r="B10" t="n">
-        <v>57632</v>
+        <v>91184</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784380</v>
+        <v>784340</v>
       </c>
       <c r="R10" t="n">
-        <v>7286228</v>
+        <v>7286230</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125205937</v>
+        <v>125205961</v>
       </c>
       <c r="B11" t="n">
-        <v>97147</v>
+        <v>96395</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,21 +1627,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1682,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784359</v>
+        <v>784461</v>
       </c>
       <c r="R11" t="n">
-        <v>7286440</v>
+        <v>7286446</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125205952</v>
+        <v>125205944</v>
       </c>
       <c r="B12" t="n">
-        <v>82737</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,21 +1729,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1784,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784330</v>
+        <v>784323</v>
       </c>
       <c r="R12" t="n">
-        <v>7286266</v>
+        <v>7286284</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125201648</v>
+        <v>125205943</v>
       </c>
       <c r="B13" t="n">
-        <v>91617</v>
+        <v>91184</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,38 +1827,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>784333</v>
+        <v>784323</v>
       </c>
       <c r="R13" t="n">
-        <v>7286210</v>
+        <v>7286243</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,11 +1893,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gran bark kvar</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1941,22 +1905,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125201638</v>
+        <v>125205925</v>
       </c>
       <c r="B14" t="n">
-        <v>78979</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,34 +1933,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>784464</v>
+        <v>784312</v>
       </c>
       <c r="R14" t="n">
-        <v>7286498</v>
+        <v>7286305</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2026,9 +2006,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2043,22 +2033,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125205953</v>
+        <v>125205951</v>
       </c>
       <c r="B15" t="n">
-        <v>57053</v>
+        <v>82737</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,46 +2057,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102954</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>784304</v>
+        <v>784382</v>
       </c>
       <c r="R15" t="n">
-        <v>7286278</v>
+        <v>7286215</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,19 +2118,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2175,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125205958</v>
+        <v>125205937</v>
       </c>
       <c r="B16" t="n">
-        <v>75017</v>
+        <v>97147</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,25 +2159,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2215,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>784424</v>
+        <v>784359</v>
       </c>
       <c r="R16" t="n">
-        <v>7286482</v>
+        <v>7286440</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,10 +2249,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125205961</v>
+        <v>125201638</v>
       </c>
       <c r="B17" t="n">
-        <v>96395</v>
+        <v>78979</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,38 +2261,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>784461</v>
+        <v>784464</v>
       </c>
       <c r="R17" t="n">
-        <v>7286446</v>
+        <v>7286498</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,22 +2339,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125205959</v>
+        <v>125205953</v>
       </c>
       <c r="B18" t="n">
-        <v>96395</v>
+        <v>57053</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2395,34 +2367,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>102954</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>784478</v>
+        <v>784304</v>
       </c>
       <c r="R18" t="n">
-        <v>7286475</v>
+        <v>7286278</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,9 +2432,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,10 +2573,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125205928</v>
+        <v>125205958</v>
       </c>
       <c r="B20" t="n">
-        <v>57793</v>
+        <v>75017</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,42 +2589,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>784295</v>
+        <v>784424</v>
       </c>
       <c r="R20" t="n">
-        <v>7286331</v>
+        <v>7286482</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,19 +2646,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,10 +2675,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125205942</v>
+        <v>125205938</v>
       </c>
       <c r="B21" t="n">
-        <v>91184</v>
+        <v>97147</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2715,25 +2687,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>784340</v>
+        <v>784387</v>
       </c>
       <c r="R21" t="n">
-        <v>7286230</v>
+        <v>7286256</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,10 +2777,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125205944</v>
+        <v>125205932</v>
       </c>
       <c r="B22" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,21 +2793,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2817,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>784323</v>
+        <v>784380</v>
       </c>
       <c r="R22" t="n">
-        <v>7286284</v>
+        <v>7286228</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,10 +2879,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125201677</v>
+        <v>125205941</v>
       </c>
       <c r="B23" t="n">
-        <v>82737</v>
+        <v>91184</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,34 +2895,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>784276</v>
+        <v>784331</v>
       </c>
       <c r="R23" t="n">
-        <v>7286135</v>
+        <v>7286390</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,22 +2969,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125205921</v>
+        <v>125205931</v>
       </c>
       <c r="B24" t="n">
-        <v>91131</v>
+        <v>57632</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3021,38 +2993,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>784282</v>
+        <v>784313</v>
       </c>
       <c r="R24" t="n">
-        <v>7286280</v>
+        <v>7286297</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3082,9 +3062,24 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3111,10 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125205956</v>
+        <v>125205936</v>
       </c>
       <c r="B25" t="n">
-        <v>57053</v>
+        <v>97147</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3127,42 +3122,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102954</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>784280</v>
+        <v>784312</v>
       </c>
       <c r="R25" t="n">
-        <v>7286150</v>
+        <v>7286355</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,19 +3179,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3231,10 +3208,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125205936</v>
+        <v>125201648</v>
       </c>
       <c r="B26" t="n">
-        <v>97147</v>
+        <v>91617</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3243,38 +3220,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>784312</v>
+        <v>784333</v>
       </c>
       <c r="R26" t="n">
-        <v>7286355</v>
+        <v>7286210</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3309,6 +3286,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gran bark kvar</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3321,22 +3303,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125205943</v>
+        <v>125205949</v>
       </c>
       <c r="B27" t="n">
-        <v>91184</v>
+        <v>82737</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3349,21 +3331,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3376,7 +3358,7 @@
         <v>784323</v>
       </c>
       <c r="R27" t="n">
-        <v>7286243</v>
+        <v>7286372</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,7 +3417,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125205948</v>
+        <v>125201677</v>
       </c>
       <c r="B28" t="n">
         <v>82737</v>
@@ -3471,14 +3453,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>784378</v>
+        <v>784276</v>
       </c>
       <c r="R28" t="n">
-        <v>7286451</v>
+        <v>7286135</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,22 +3507,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125205949</v>
+        <v>125205928</v>
       </c>
       <c r="B29" t="n">
-        <v>82737</v>
+        <v>57793</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3553,34 +3535,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>784323</v>
+        <v>784295</v>
       </c>
       <c r="R29" t="n">
-        <v>7286372</v>
+        <v>7286331</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3610,9 +3600,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3639,10 +3639,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125201671</v>
+        <v>125201679</v>
       </c>
       <c r="B30" t="n">
-        <v>82737</v>
+        <v>96395</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3651,25 +3651,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>784334</v>
+        <v>784366</v>
       </c>
       <c r="R30" t="n">
-        <v>7286197</v>
+        <v>7286457</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125201678</v>
+        <v>125201670</v>
       </c>
       <c r="B31" t="n">
-        <v>96395</v>
+        <v>82737</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3753,25 +3753,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>784473</v>
+        <v>784308</v>
       </c>
       <c r="R31" t="n">
-        <v>7286440</v>
+        <v>7286195</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,10 +3843,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125201679</v>
+        <v>125201671</v>
       </c>
       <c r="B32" t="n">
-        <v>96395</v>
+        <v>82737</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3855,25 +3855,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>784366</v>
+        <v>784334</v>
       </c>
       <c r="R32" t="n">
-        <v>7286457</v>
+        <v>7286197</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,10 +3945,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125201670</v>
+        <v>125201678</v>
       </c>
       <c r="B33" t="n">
-        <v>82737</v>
+        <v>96395</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3957,25 +3957,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>784308</v>
+        <v>784473</v>
       </c>
       <c r="R33" t="n">
-        <v>7286195</v>
+        <v>7286440</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4047,10 +4047,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125201635</v>
+        <v>125201645</v>
       </c>
       <c r="B34" t="n">
-        <v>75025</v>
+        <v>91166</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>784271</v>
+        <v>784360</v>
       </c>
       <c r="R34" t="n">
-        <v>7286137</v>
+        <v>7286237</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4123,11 +4123,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På levande gran, +200, grå/vitt substrat,</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4154,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125201657</v>
+        <v>125201655</v>
       </c>
       <c r="B35" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4166,25 +4161,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4194,10 +4189,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>784313</v>
+        <v>784464</v>
       </c>
       <c r="R35" t="n">
-        <v>7286311</v>
+        <v>7286450</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4256,10 +4251,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125201641</v>
+        <v>125201639</v>
       </c>
       <c r="B36" t="n">
-        <v>91166</v>
+        <v>91131</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4268,25 +4263,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4296,10 +4291,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>784273</v>
+        <v>784305</v>
       </c>
       <c r="R36" t="n">
-        <v>7286260</v>
+        <v>7286333</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4358,10 +4353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125201645</v>
+        <v>125201660</v>
       </c>
       <c r="B37" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4374,21 +4369,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4398,10 +4393,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>784360</v>
+        <v>784394</v>
       </c>
       <c r="R37" t="n">
-        <v>7286237</v>
+        <v>7286334</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4460,7 +4455,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125201646</v>
+        <v>125201644</v>
       </c>
       <c r="B38" t="n">
         <v>91166</v>
@@ -4500,10 +4495,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>784324</v>
+        <v>784368</v>
       </c>
       <c r="R38" t="n">
-        <v>7286201</v>
+        <v>7286235</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4562,10 +4557,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125201666</v>
+        <v>125201640</v>
       </c>
       <c r="B39" t="n">
-        <v>82737</v>
+        <v>91166</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4578,21 +4573,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4602,10 +4597,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>784339</v>
+        <v>784265</v>
       </c>
       <c r="R39" t="n">
-        <v>7286244</v>
+        <v>7286257</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4664,10 +4659,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125201659</v>
+        <v>125201646</v>
       </c>
       <c r="B40" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4680,21 +4675,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4704,10 +4699,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>784312</v>
+        <v>784324</v>
       </c>
       <c r="R40" t="n">
-        <v>7286315</v>
+        <v>7286201</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4766,10 +4761,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125201636</v>
+        <v>125201641</v>
       </c>
       <c r="B41" t="n">
-        <v>75025</v>
+        <v>91166</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4782,21 +4777,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4806,10 +4801,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>784334</v>
+        <v>784273</v>
       </c>
       <c r="R41" t="n">
-        <v>7286242</v>
+        <v>7286260</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4868,10 +4863,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125201644</v>
+        <v>125201663</v>
       </c>
       <c r="B42" t="n">
-        <v>91166</v>
+        <v>82737</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4884,21 +4879,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4908,10 +4903,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>784368</v>
+        <v>784333</v>
       </c>
       <c r="R42" t="n">
-        <v>7286235</v>
+        <v>7286405</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4970,10 +4965,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125201664</v>
+        <v>125201636</v>
       </c>
       <c r="B43" t="n">
-        <v>82737</v>
+        <v>75025</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4986,21 +4981,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5010,10 +5005,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>784378</v>
+        <v>784334</v>
       </c>
       <c r="R43" t="n">
-        <v>7286354</v>
+        <v>7286242</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5072,7 +5067,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125201661</v>
+        <v>125201659</v>
       </c>
       <c r="B44" t="n">
         <v>78947</v>
@@ -5112,10 +5107,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>784347</v>
+        <v>784312</v>
       </c>
       <c r="R44" t="n">
-        <v>7286236</v>
+        <v>7286315</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5174,10 +5169,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125201655</v>
+        <v>125201656</v>
       </c>
       <c r="B45" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5186,25 +5181,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5214,10 +5209,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>784464</v>
+        <v>784313</v>
       </c>
       <c r="R45" t="n">
-        <v>7286450</v>
+        <v>7286267</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5276,10 +5271,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125201668</v>
+        <v>125201657</v>
       </c>
       <c r="B46" t="n">
-        <v>82737</v>
+        <v>78947</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5292,21 +5287,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5316,10 +5311,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>784327</v>
+        <v>784313</v>
       </c>
       <c r="R46" t="n">
-        <v>7286212</v>
+        <v>7286311</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5378,10 +5373,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125201642</v>
+        <v>125201667</v>
       </c>
       <c r="B47" t="n">
-        <v>91166</v>
+        <v>82737</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5394,21 +5389,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5418,10 +5413,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>784349</v>
+        <v>784327</v>
       </c>
       <c r="R47" t="n">
-        <v>7286343</v>
+        <v>7286212</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5480,10 +5475,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125201639</v>
+        <v>125201642</v>
       </c>
       <c r="B48" t="n">
-        <v>91131</v>
+        <v>91166</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5492,25 +5487,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5520,10 +5515,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>784305</v>
+        <v>784349</v>
       </c>
       <c r="R48" t="n">
-        <v>7286333</v>
+        <v>7286343</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5582,10 +5577,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125201640</v>
+        <v>125201650</v>
       </c>
       <c r="B49" t="n">
-        <v>91166</v>
+        <v>91459</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5598,21 +5593,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5622,10 +5617,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>784265</v>
+        <v>784257</v>
       </c>
       <c r="R49" t="n">
-        <v>7286257</v>
+        <v>7286240</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5684,10 +5679,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125201650</v>
+        <v>125201637</v>
       </c>
       <c r="B50" t="n">
-        <v>91459</v>
+        <v>75025</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5700,21 +5695,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5724,10 +5719,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>784257</v>
+        <v>784286</v>
       </c>
       <c r="R50" t="n">
-        <v>7286240</v>
+        <v>7286144</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5786,10 +5781,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125201660</v>
+        <v>125201666</v>
       </c>
       <c r="B51" t="n">
-        <v>78947</v>
+        <v>82737</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5802,21 +5797,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5826,10 +5821,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>784394</v>
+        <v>784339</v>
       </c>
       <c r="R51" t="n">
-        <v>7286334</v>
+        <v>7286244</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5888,10 +5883,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125201637</v>
+        <v>125201664</v>
       </c>
       <c r="B52" t="n">
-        <v>75025</v>
+        <v>82737</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5904,21 +5899,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5928,10 +5923,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>784286</v>
+        <v>784378</v>
       </c>
       <c r="R52" t="n">
-        <v>7286144</v>
+        <v>7286354</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5990,7 +5985,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125201656</v>
+        <v>125201661</v>
       </c>
       <c r="B53" t="n">
         <v>78947</v>
@@ -6030,10 +6025,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>784313</v>
+        <v>784347</v>
       </c>
       <c r="R53" t="n">
-        <v>7286267</v>
+        <v>7286236</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6092,10 +6087,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125201663</v>
+        <v>125201635</v>
       </c>
       <c r="B54" t="n">
-        <v>82737</v>
+        <v>75025</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6108,21 +6103,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6132,10 +6127,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>784333</v>
+        <v>784271</v>
       </c>
       <c r="R54" t="n">
-        <v>7286405</v>
+        <v>7286137</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6168,6 +6163,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På levande gran, +200, grå/vitt substrat,</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125205945</v>
+        <v>125205959</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
+        <v>96395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784321</v>
+        <v>784478</v>
       </c>
       <c r="R3" t="n">
-        <v>7286252</v>
+        <v>7286475</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125205959</v>
+        <v>125205948</v>
       </c>
       <c r="B4" t="n">
-        <v>96395</v>
+        <v>82737</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784478</v>
+        <v>784378</v>
       </c>
       <c r="R4" t="n">
-        <v>7286475</v>
+        <v>7286451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125205948</v>
+        <v>125205945</v>
       </c>
       <c r="B5" t="n">
-        <v>82737</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784378</v>
+        <v>784321</v>
       </c>
       <c r="R5" t="n">
-        <v>7286451</v>
+        <v>7286252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2249,10 +2249,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125201638</v>
+        <v>125205953</v>
       </c>
       <c r="B17" t="n">
-        <v>78979</v>
+        <v>57053</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2261,38 +2261,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>102954</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>784464</v>
+        <v>784304</v>
       </c>
       <c r="R17" t="n">
-        <v>7286498</v>
+        <v>7286278</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,9 +2330,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2339,22 +2357,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125205953</v>
+        <v>125201638</v>
       </c>
       <c r="B18" t="n">
-        <v>57053</v>
+        <v>78979</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2363,46 +2381,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102954</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>784304</v>
+        <v>784464</v>
       </c>
       <c r="R18" t="n">
-        <v>7286278</v>
+        <v>7286498</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2432,19 +2442,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2459,12 +2459,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -5577,10 +5577,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125201650</v>
+        <v>125201637</v>
       </c>
       <c r="B49" t="n">
-        <v>91459</v>
+        <v>75025</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5593,21 +5593,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>784257</v>
+        <v>784286</v>
       </c>
       <c r="R49" t="n">
-        <v>7286240</v>
+        <v>7286144</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5679,10 +5679,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125201637</v>
+        <v>125201650</v>
       </c>
       <c r="B50" t="n">
-        <v>75025</v>
+        <v>91459</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5695,21 +5695,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>784286</v>
+        <v>784257</v>
       </c>
       <c r="R50" t="n">
-        <v>7286144</v>
+        <v>7286240</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125205950</v>
+        <v>125205958</v>
       </c>
       <c r="B2" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75058</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>784389</v>
+        <v>784424</v>
       </c>
       <c r="R2" t="n">
-        <v>7286301</v>
+        <v>7286482</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125205959</v>
+        <v>125205932</v>
       </c>
       <c r="B3" t="n">
-        <v>96395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784478</v>
+        <v>784380</v>
       </c>
       <c r="R3" t="n">
-        <v>7286475</v>
+        <v>7286228</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125205948</v>
+        <v>125205921</v>
       </c>
       <c r="B4" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784378</v>
+        <v>784282</v>
       </c>
       <c r="R4" t="n">
-        <v>7286451</v>
+        <v>7286280</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125205945</v>
+        <v>125205948</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784321</v>
+        <v>784378</v>
       </c>
       <c r="R5" t="n">
-        <v>7286252</v>
+        <v>7286451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125205939</v>
+        <v>125205956</v>
       </c>
       <c r="B6" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57063</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,16 +1074,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>102954</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1117,16 +1092,24 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784306</v>
+        <v>784280</v>
       </c>
       <c r="R6" t="n">
-        <v>7286218</v>
+        <v>7286150</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,9 +1139,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,15 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125205956</v>
+        <v>125205937</v>
       </c>
       <c r="B7" t="n">
-        <v>57053</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,42 +1189,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102954</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784280</v>
+        <v>784359</v>
       </c>
       <c r="R7" t="n">
-        <v>7286150</v>
+        <v>7286440</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,19 +1246,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,15 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125205921</v>
+        <v>125205938</v>
       </c>
       <c r="B8" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1321,21 +1286,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>784282</v>
+        <v>784387</v>
       </c>
       <c r="R8" t="n">
-        <v>7286280</v>
+        <v>7286256</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,15 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125205952</v>
+        <v>125205931</v>
       </c>
       <c r="B9" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,34 +1383,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>784330</v>
+        <v>784313</v>
       </c>
       <c r="R9" t="n">
-        <v>7286266</v>
+        <v>7286297</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,9 +1448,24 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,15 +1492,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125205942</v>
+        <v>125205941</v>
       </c>
       <c r="B10" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,10 +1527,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784340</v>
+        <v>784331</v>
       </c>
       <c r="R10" t="n">
-        <v>7286230</v>
+        <v>7286390</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,50 +1589,61 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125205961</v>
+        <v>125205925</v>
       </c>
       <c r="B11" t="n">
-        <v>96395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784461</v>
+        <v>784312</v>
       </c>
       <c r="R11" t="n">
-        <v>7286446</v>
+        <v>7286305</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,9 +1673,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1713,15 +1712,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125205944</v>
+        <v>125201638</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78999</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1729,34 +1723,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784323</v>
+        <v>784464</v>
       </c>
       <c r="R12" t="n">
-        <v>7286284</v>
+        <v>7286498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,62 +1797,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125205943</v>
+        <v>125201648</v>
       </c>
       <c r="B13" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91671</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>784323</v>
+        <v>784333</v>
       </c>
       <c r="R13" t="n">
-        <v>7286243</v>
+        <v>7286210</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,6 +1882,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gran bark kvar</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1905,27 +1899,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125205925</v>
+        <v>125205944</v>
       </c>
       <c r="B14" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1933,50 +1922,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>784312</v>
+        <v>784323</v>
       </c>
       <c r="R14" t="n">
-        <v>7286305</v>
+        <v>7286284</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,19 +1979,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>17:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2045,37 +2008,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125205951</v>
+        <v>125205939</v>
       </c>
       <c r="B15" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58019</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2085,10 +2043,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>784382</v>
+        <v>784306</v>
       </c>
       <c r="R15" t="n">
-        <v>7286215</v>
+        <v>7286218</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,37 +2105,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125205937</v>
+        <v>125205952</v>
       </c>
       <c r="B16" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2187,10 +2140,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>784359</v>
+        <v>784330</v>
       </c>
       <c r="R16" t="n">
-        <v>7286440</v>
+        <v>7286266</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,58 +2202,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125205953</v>
+        <v>125205942</v>
       </c>
       <c r="B17" t="n">
-        <v>57053</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102954</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>784304</v>
+        <v>784340</v>
       </c>
       <c r="R17" t="n">
-        <v>7286278</v>
+        <v>7286230</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,19 +2270,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2369,50 +2299,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125201638</v>
+        <v>125205961</v>
       </c>
       <c r="B18" t="n">
-        <v>78979</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>784464</v>
+        <v>784461</v>
       </c>
       <c r="R18" t="n">
-        <v>7286498</v>
+        <v>7286446</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2459,12 +2384,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2474,12 +2399,7 @@
         <v>125205935</v>
       </c>
       <c r="B19" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,37 +2493,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125205958</v>
+        <v>125205936</v>
       </c>
       <c r="B20" t="n">
-        <v>75017</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2613,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>784424</v>
+        <v>784312</v>
       </c>
       <c r="R20" t="n">
-        <v>7286482</v>
+        <v>7286355</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2675,15 +2590,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125205938</v>
+        <v>125205953</v>
       </c>
       <c r="B21" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57063</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,34 +2601,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>102954</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>784387</v>
+        <v>784304</v>
       </c>
       <c r="R21" t="n">
-        <v>7286256</v>
+        <v>7286278</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2748,9 +2666,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2777,15 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125205932</v>
+        <v>125205950</v>
       </c>
       <c r="B22" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2793,21 +2716,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2817,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>784380</v>
+        <v>784389</v>
       </c>
       <c r="R22" t="n">
-        <v>7286228</v>
+        <v>7286301</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2879,15 +2802,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125205941</v>
+        <v>125205928</v>
       </c>
       <c r="B23" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2895,34 +2813,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>784331</v>
+        <v>784295</v>
       </c>
       <c r="R23" t="n">
-        <v>7286390</v>
+        <v>7286331</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2952,9 +2878,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2981,15 +2917,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125205931</v>
+        <v>125205951</v>
       </c>
       <c r="B24" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2997,42 +2928,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>784313</v>
+        <v>784382</v>
       </c>
       <c r="R24" t="n">
-        <v>7286297</v>
+        <v>7286215</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3062,24 +2985,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,37 +3014,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125205936</v>
+        <v>125205945</v>
       </c>
       <c r="B25" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3146,10 +3049,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>784312</v>
+        <v>784321</v>
       </c>
       <c r="R25" t="n">
-        <v>7286355</v>
+        <v>7286252</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3208,50 +3111,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125201648</v>
+        <v>125205949</v>
       </c>
       <c r="B26" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>784333</v>
+        <v>784323</v>
       </c>
       <c r="R26" t="n">
-        <v>7286210</v>
+        <v>7286372</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3286,11 +3184,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gran bark kvar</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3303,27 +3196,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125205949</v>
+        <v>125205943</v>
       </c>
       <c r="B27" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3331,21 +3219,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3358,7 +3246,7 @@
         <v>784323</v>
       </c>
       <c r="R27" t="n">
-        <v>7286372</v>
+        <v>7286243</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3417,50 +3305,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125201677</v>
+        <v>125205959</v>
       </c>
       <c r="B28" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>784276</v>
+        <v>784478</v>
       </c>
       <c r="R28" t="n">
-        <v>7286135</v>
+        <v>7286475</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3507,27 +3390,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125205928</v>
+        <v>125201677</v>
       </c>
       <c r="B29" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3535,42 +3413,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>784295</v>
+        <v>784276</v>
       </c>
       <c r="R29" t="n">
-        <v>7286331</v>
+        <v>7286135</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3600,19 +3470,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3627,49 +3487,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125201679</v>
+        <v>125201671</v>
       </c>
       <c r="B30" t="n">
-        <v>96395</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3679,10 +3534,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>784366</v>
+        <v>784334</v>
       </c>
       <c r="R30" t="n">
-        <v>7286457</v>
+        <v>7286197</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,37 +3596,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125201670</v>
+        <v>125201678</v>
       </c>
       <c r="B31" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3781,10 +3631,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>784308</v>
+        <v>784473</v>
       </c>
       <c r="R31" t="n">
-        <v>7286195</v>
+        <v>7286440</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,37 +3693,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125201671</v>
+        <v>125201679</v>
       </c>
       <c r="B32" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3883,10 +3728,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>784334</v>
+        <v>784366</v>
       </c>
       <c r="R32" t="n">
-        <v>7286197</v>
+        <v>7286457</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,37 +3790,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125201678</v>
+        <v>125201670</v>
       </c>
       <c r="B33" t="n">
-        <v>96395</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3985,10 +3825,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>784473</v>
+        <v>784308</v>
       </c>
       <c r="R33" t="n">
-        <v>7286440</v>
+        <v>7286195</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4047,15 +3887,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125201645</v>
+        <v>125201644</v>
       </c>
       <c r="B34" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4087,10 +3922,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>784360</v>
+        <v>784368</v>
       </c>
       <c r="R34" t="n">
-        <v>7286237</v>
+        <v>7286235</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4149,37 +3984,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125201655</v>
+        <v>125201668</v>
       </c>
       <c r="B35" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4189,10 +4019,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>784464</v>
+        <v>784327</v>
       </c>
       <c r="R35" t="n">
-        <v>7286450</v>
+        <v>7286212</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4251,37 +4081,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125201639</v>
+        <v>125201645</v>
       </c>
       <c r="B36" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4291,10 +4116,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>784305</v>
+        <v>784360</v>
       </c>
       <c r="R36" t="n">
-        <v>7286333</v>
+        <v>7286237</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4353,15 +4178,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125201660</v>
+        <v>125201636</v>
       </c>
       <c r="B37" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75066</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4369,21 +4189,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4393,10 +4213,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>784394</v>
+        <v>784334</v>
       </c>
       <c r="R37" t="n">
-        <v>7286334</v>
+        <v>7286242</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4455,15 +4275,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125201644</v>
+        <v>125201663</v>
       </c>
       <c r="B38" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4471,21 +4286,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4495,10 +4310,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>784368</v>
+        <v>784333</v>
       </c>
       <c r="R38" t="n">
-        <v>7286235</v>
+        <v>7286405</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4557,15 +4372,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125201640</v>
+        <v>125201635</v>
       </c>
       <c r="B39" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75066</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4573,21 +4383,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4597,10 +4407,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>784265</v>
+        <v>784271</v>
       </c>
       <c r="R39" t="n">
-        <v>7286257</v>
+        <v>7286137</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4633,6 +4443,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På levande gran, +200, grå/vitt substrat,</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4659,15 +4474,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125201646</v>
+        <v>125201657</v>
       </c>
       <c r="B40" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,21 +4485,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4699,10 +4509,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>784324</v>
+        <v>784313</v>
       </c>
       <c r="R40" t="n">
-        <v>7286201</v>
+        <v>7286311</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4761,37 +4571,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125201641</v>
+        <v>125201655</v>
       </c>
       <c r="B41" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4801,10 +4606,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>784273</v>
+        <v>784464</v>
       </c>
       <c r="R41" t="n">
-        <v>7286260</v>
+        <v>7286450</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4863,15 +4668,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125201663</v>
+        <v>125201664</v>
       </c>
       <c r="B42" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4903,10 +4703,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>784333</v>
+        <v>784378</v>
       </c>
       <c r="R42" t="n">
-        <v>7286405</v>
+        <v>7286354</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4965,15 +4765,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125201636</v>
+        <v>125201637</v>
       </c>
       <c r="B43" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75066</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5005,10 +4800,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>784334</v>
+        <v>784286</v>
       </c>
       <c r="R43" t="n">
-        <v>7286242</v>
+        <v>7286144</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5067,15 +4862,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125201659</v>
+        <v>125201656</v>
       </c>
       <c r="B44" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5107,10 +4897,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>784312</v>
+        <v>784313</v>
       </c>
       <c r="R44" t="n">
-        <v>7286315</v>
+        <v>7286267</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5169,15 +4959,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125201656</v>
+        <v>125201646</v>
       </c>
       <c r="B45" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5185,21 +4970,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5209,10 +4994,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>784313</v>
+        <v>784324</v>
       </c>
       <c r="R45" t="n">
-        <v>7286267</v>
+        <v>7286201</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5271,15 +5056,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125201657</v>
+        <v>125201659</v>
       </c>
       <c r="B46" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5311,10 +5091,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>784313</v>
+        <v>784312</v>
       </c>
       <c r="R46" t="n">
-        <v>7286311</v>
+        <v>7286315</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5373,15 +5153,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125201667</v>
+        <v>125201660</v>
       </c>
       <c r="B47" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5389,21 +5164,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5413,10 +5188,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>784327</v>
+        <v>784394</v>
       </c>
       <c r="R47" t="n">
-        <v>7286212</v>
+        <v>7286334</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5475,15 +5250,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125201642</v>
+        <v>125201661</v>
       </c>
       <c r="B48" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5491,21 +5261,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5515,10 +5285,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>784349</v>
+        <v>784347</v>
       </c>
       <c r="R48" t="n">
-        <v>7286343</v>
+        <v>7286236</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5577,15 +5347,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125201637</v>
+        <v>125201650</v>
       </c>
       <c r="B49" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5593,21 +5358,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5617,10 +5382,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>784286</v>
+        <v>784257</v>
       </c>
       <c r="R49" t="n">
-        <v>7286144</v>
+        <v>7286240</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5679,15 +5444,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125201650</v>
+        <v>125201642</v>
       </c>
       <c r="B50" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5695,21 +5455,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5719,10 +5479,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>784257</v>
+        <v>784349</v>
       </c>
       <c r="R50" t="n">
-        <v>7286240</v>
+        <v>7286343</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5781,37 +5541,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125201666</v>
+        <v>125201639</v>
       </c>
       <c r="B51" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5821,10 +5576,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>784339</v>
+        <v>784305</v>
       </c>
       <c r="R51" t="n">
-        <v>7286244</v>
+        <v>7286333</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5883,15 +5638,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125201664</v>
+        <v>125201640</v>
       </c>
       <c r="B52" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5899,21 +5649,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5923,10 +5673,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>784378</v>
+        <v>784265</v>
       </c>
       <c r="R52" t="n">
-        <v>7286354</v>
+        <v>7286257</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5985,15 +5735,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125201661</v>
+        <v>125201641</v>
       </c>
       <c r="B53" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6001,21 +5746,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6025,10 +5770,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>784347</v>
+        <v>784273</v>
       </c>
       <c r="R53" t="n">
-        <v>7286236</v>
+        <v>7286260</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6087,15 +5832,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125201635</v>
+        <v>125201666</v>
       </c>
       <c r="B54" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6103,21 +5843,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6127,10 +5867,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>784271</v>
+        <v>784339</v>
       </c>
       <c r="R54" t="n">
-        <v>7286137</v>
+        <v>7286244</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6163,11 +5903,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På levande gran, +200, grå/vitt substrat,</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -1178,45 +1178,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125205937</v>
+        <v>125205931</v>
       </c>
       <c r="B7" t="n">
-        <v>97202</v>
+        <v>57648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784359</v>
+        <v>784313</v>
       </c>
       <c r="R7" t="n">
-        <v>7286440</v>
+        <v>7286297</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,9 +1254,24 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,7 +1298,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125205938</v>
+        <v>125205937</v>
       </c>
       <c r="B8" t="n">
         <v>97202</v>
@@ -1310,10 +1333,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>784387</v>
+        <v>784359</v>
       </c>
       <c r="R8" t="n">
-        <v>7286256</v>
+        <v>7286440</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,53 +1395,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125205931</v>
+        <v>125205938</v>
       </c>
       <c r="B9" t="n">
-        <v>57648</v>
+        <v>97202</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>784313</v>
+        <v>784387</v>
       </c>
       <c r="R9" t="n">
-        <v>7286297</v>
+        <v>7286256</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1448,24 +1463,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1589,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125205925</v>
+        <v>125201638</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>78999</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1600,50 +1600,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784312</v>
+        <v>784464</v>
       </c>
       <c r="R11" t="n">
-        <v>7286305</v>
+        <v>7286498</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,19 +1657,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,44 +1674,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125201638</v>
+        <v>125201648</v>
       </c>
       <c r="B12" t="n">
-        <v>78999</v>
+        <v>91671</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1721,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784464</v>
+        <v>784333</v>
       </c>
       <c r="R12" t="n">
-        <v>7286498</v>
+        <v>7286210</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1783,6 +1757,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gran bark kvar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,45 +1788,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125201648</v>
+        <v>125205925</v>
       </c>
       <c r="B13" t="n">
-        <v>91671</v>
+        <v>57651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>784333</v>
+        <v>784312</v>
       </c>
       <c r="R13" t="n">
-        <v>7286210</v>
+        <v>7286305</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1877,14 +1872,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gran bark kvar</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,44 +1899,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125205944</v>
+        <v>125205939</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>58019</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>784323</v>
+        <v>784306</v>
       </c>
       <c r="R14" t="n">
-        <v>7286284</v>
+        <v>7286218</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,32 +2008,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125205939</v>
+        <v>125205944</v>
       </c>
       <c r="B15" t="n">
-        <v>58019</v>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>784306</v>
+        <v>784323</v>
       </c>
       <c r="R15" t="n">
-        <v>7286218</v>
+        <v>7286284</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125205952</v>
+        <v>125205935</v>
       </c>
       <c r="B16" t="n">
-        <v>82779</v>
+        <v>91513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2116,21 +2116,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>784330</v>
+        <v>784264</v>
       </c>
       <c r="R16" t="n">
-        <v>7286266</v>
+        <v>7286244</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,10 +2202,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125205942</v>
+        <v>125205952</v>
       </c>
       <c r="B17" t="n">
-        <v>91238</v>
+        <v>82779</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>784340</v>
+        <v>784330</v>
       </c>
       <c r="R17" t="n">
-        <v>7286230</v>
+        <v>7286266</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2299,32 +2299,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125205961</v>
+        <v>125205942</v>
       </c>
       <c r="B18" t="n">
-        <v>96450</v>
+        <v>91238</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>784461</v>
+        <v>784340</v>
       </c>
       <c r="R18" t="n">
-        <v>7286446</v>
+        <v>7286230</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2396,32 +2396,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125205935</v>
+        <v>125205961</v>
       </c>
       <c r="B19" t="n">
-        <v>91513</v>
+        <v>96450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>784264</v>
+        <v>784461</v>
       </c>
       <c r="R19" t="n">
-        <v>7286244</v>
+        <v>7286446</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125205928</v>
+        <v>125205951</v>
       </c>
       <c r="B23" t="n">
-        <v>57811</v>
+        <v>82779</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2813,42 +2813,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>784295</v>
+        <v>784382</v>
       </c>
       <c r="R23" t="n">
-        <v>7286331</v>
+        <v>7286215</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2878,19 +2870,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2917,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125205951</v>
+        <v>125205928</v>
       </c>
       <c r="B24" t="n">
-        <v>82779</v>
+        <v>57811</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2928,34 +2910,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>784382</v>
+        <v>784295</v>
       </c>
       <c r="R24" t="n">
-        <v>7286215</v>
+        <v>7286331</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2985,9 +2975,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4474,32 +4474,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125201657</v>
+        <v>125201655</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>98324</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>784313</v>
+        <v>784464</v>
       </c>
       <c r="R40" t="n">
-        <v>7286311</v>
+        <v>7286450</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4571,32 +4571,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125201655</v>
+        <v>125201657</v>
       </c>
       <c r="B41" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>784464</v>
+        <v>784313</v>
       </c>
       <c r="R41" t="n">
-        <v>7286450</v>
+        <v>7286311</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5541,32 +5541,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125201639</v>
+        <v>125201640</v>
       </c>
       <c r="B51" t="n">
-        <v>91185</v>
+        <v>91220</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>784305</v>
+        <v>784265</v>
       </c>
       <c r="R51" t="n">
-        <v>7286333</v>
+        <v>7286257</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125201640</v>
+        <v>125201641</v>
       </c>
       <c r="B52" t="n">
         <v>91220</v>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>784265</v>
+        <v>784273</v>
       </c>
       <c r="R52" t="n">
-        <v>7286257</v>
+        <v>7286260</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125201641</v>
+        <v>125201666</v>
       </c>
       <c r="B53" t="n">
-        <v>91220</v>
+        <v>82779</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>784273</v>
+        <v>784339</v>
       </c>
       <c r="R53" t="n">
-        <v>7286260</v>
+        <v>7286244</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5832,32 +5832,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125201666</v>
+        <v>125201639</v>
       </c>
       <c r="B54" t="n">
-        <v>82779</v>
+        <v>91185</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>784339</v>
+        <v>784305</v>
       </c>
       <c r="R54" t="n">
-        <v>7286244</v>
+        <v>7286333</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125205932</v>
+        <v>125205948</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
+        <v>82779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784380</v>
+        <v>784378</v>
       </c>
       <c r="R3" t="n">
-        <v>7286228</v>
+        <v>7286451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>125205921</v>
       </c>
       <c r="B4" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125205948</v>
+        <v>125205932</v>
       </c>
       <c r="B5" t="n">
-        <v>82779</v>
+        <v>57648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784378</v>
+        <v>784380</v>
       </c>
       <c r="R5" t="n">
-        <v>7286451</v>
+        <v>7286228</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,27 +1063,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125205956</v>
+        <v>125205931</v>
       </c>
       <c r="B6" t="n">
-        <v>57063</v>
+        <v>57648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102954</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1096,7 +1096,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784280</v>
+        <v>784313</v>
       </c>
       <c r="R6" t="n">
-        <v>7286150</v>
+        <v>7286297</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1151,7 +1151,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,27 +1183,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125205931</v>
+        <v>125205956</v>
       </c>
       <c r="B7" t="n">
-        <v>57648</v>
+        <v>57063</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1211,7 +1216,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1221,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784313</v>
+        <v>784280</v>
       </c>
       <c r="R7" t="n">
-        <v>7286297</v>
+        <v>7286150</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,7 +1261,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1266,12 +1271,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackläte</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,7 +1301,7 @@
         <v>125205937</v>
       </c>
       <c r="B8" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>125205938</v>
       </c>
       <c r="B9" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>125205941</v>
       </c>
       <c r="B10" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125201638</v>
+        <v>125205925</v>
       </c>
       <c r="B11" t="n">
-        <v>78999</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1600,34 +1600,50 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784464</v>
+        <v>784312</v>
       </c>
       <c r="R11" t="n">
-        <v>7286498</v>
+        <v>7286305</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,9 +1673,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1674,44 +1700,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125201648</v>
+        <v>125201638</v>
       </c>
       <c r="B12" t="n">
-        <v>91671</v>
+        <v>78999</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1721,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784333</v>
+        <v>784464</v>
       </c>
       <c r="R12" t="n">
-        <v>7286210</v>
+        <v>7286498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,11 +1783,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gran bark kvar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1788,61 +1809,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125205925</v>
+        <v>125201648</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>91678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>784312</v>
+        <v>784333</v>
       </c>
       <c r="R13" t="n">
-        <v>7286305</v>
+        <v>7286210</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1872,19 +1877,14 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>17:11</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gran bark kvar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,44 +1899,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125205939</v>
+        <v>125205944</v>
       </c>
       <c r="B14" t="n">
-        <v>58019</v>
+        <v>78967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>784306</v>
+        <v>784323</v>
       </c>
       <c r="R14" t="n">
-        <v>7286218</v>
+        <v>7286284</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,32 +2008,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125205944</v>
+        <v>125205939</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>58019</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>784323</v>
+        <v>784306</v>
       </c>
       <c r="R15" t="n">
-        <v>7286284</v>
+        <v>7286218</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125205935</v>
+        <v>125205942</v>
       </c>
       <c r="B16" t="n">
-        <v>91513</v>
+        <v>91245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2116,21 +2116,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>784264</v>
+        <v>784340</v>
       </c>
       <c r="R16" t="n">
-        <v>7286244</v>
+        <v>7286230</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,32 +2202,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125205952</v>
+        <v>125205961</v>
       </c>
       <c r="B17" t="n">
-        <v>82779</v>
+        <v>96457</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>784330</v>
+        <v>784461</v>
       </c>
       <c r="R17" t="n">
-        <v>7286266</v>
+        <v>7286446</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125205942</v>
+        <v>125205935</v>
       </c>
       <c r="B18" t="n">
-        <v>91238</v>
+        <v>91520</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2310,21 +2310,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>784340</v>
+        <v>784264</v>
       </c>
       <c r="R18" t="n">
-        <v>7286230</v>
+        <v>7286244</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2396,32 +2396,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125205961</v>
+        <v>125205952</v>
       </c>
       <c r="B19" t="n">
-        <v>96450</v>
+        <v>82779</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>784461</v>
+        <v>784330</v>
       </c>
       <c r="R19" t="n">
-        <v>7286446</v>
+        <v>7286266</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2496,7 +2496,7 @@
         <v>125205936</v>
       </c>
       <c r="B20" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>125205943</v>
       </c>
       <c r="B27" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>125205959</v>
       </c>
       <c r="B28" t="n">
-        <v>96450</v>
+        <v>96457</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>125201678</v>
       </c>
       <c r="B31" t="n">
-        <v>96450</v>
+        <v>96457</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>125201679</v>
       </c>
       <c r="B32" t="n">
-        <v>96450</v>
+        <v>96457</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>125201644</v>
       </c>
       <c r="B34" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>125201645</v>
       </c>
       <c r="B36" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>125201655</v>
       </c>
       <c r="B40" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>125201646</v>
       </c>
       <c r="B45" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>125201650</v>
       </c>
       <c r="B49" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>125201642</v>
       </c>
       <c r="B50" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5541,32 +5541,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125201640</v>
+        <v>125201639</v>
       </c>
       <c r="B51" t="n">
-        <v>91220</v>
+        <v>91192</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>784265</v>
+        <v>784305</v>
       </c>
       <c r="R51" t="n">
-        <v>7286257</v>
+        <v>7286333</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5638,10 +5638,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125201641</v>
+        <v>125201640</v>
       </c>
       <c r="B52" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>784273</v>
+        <v>784265</v>
       </c>
       <c r="R52" t="n">
-        <v>7286260</v>
+        <v>7286257</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125201666</v>
+        <v>125201641</v>
       </c>
       <c r="B53" t="n">
-        <v>82779</v>
+        <v>91227</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>784339</v>
+        <v>784273</v>
       </c>
       <c r="R53" t="n">
-        <v>7286244</v>
+        <v>7286260</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5832,32 +5832,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125201639</v>
+        <v>125201666</v>
       </c>
       <c r="B54" t="n">
-        <v>91185</v>
+        <v>82779</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>784305</v>
+        <v>784339</v>
       </c>
       <c r="R54" t="n">
-        <v>7286333</v>
+        <v>7286244</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -1063,27 +1063,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125205931</v>
+        <v>125205956</v>
       </c>
       <c r="B6" t="n">
-        <v>57648</v>
+        <v>57063</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1096,7 +1096,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784313</v>
+        <v>784280</v>
       </c>
       <c r="R6" t="n">
-        <v>7286297</v>
+        <v>7286150</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1151,12 +1151,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hackläte</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,27 +1178,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125205956</v>
+        <v>125205931</v>
       </c>
       <c r="B7" t="n">
-        <v>57063</v>
+        <v>57648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102954</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1216,7 +1211,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1226,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784280</v>
+        <v>784313</v>
       </c>
       <c r="R7" t="n">
-        <v>7286150</v>
+        <v>7286297</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,7 +1256,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1271,7 +1266,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackläte</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1589,10 +1589,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125205925</v>
+        <v>125201638</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>78999</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1600,50 +1600,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyran, Strycktjärn, Nb</t>
+          <t>Långmyran- Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784312</v>
+        <v>784464</v>
       </c>
       <c r="R11" t="n">
-        <v>7286305</v>
+        <v>7286498</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,19 +1657,9 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,44 +1674,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125201638</v>
+        <v>125201648</v>
       </c>
       <c r="B12" t="n">
-        <v>78999</v>
+        <v>91678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1721,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784464</v>
+        <v>784333</v>
       </c>
       <c r="R12" t="n">
-        <v>7286498</v>
+        <v>7286210</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1783,6 +1757,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gran bark kvar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,45 +1788,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125201648</v>
+        <v>125205925</v>
       </c>
       <c r="B13" t="n">
-        <v>91678</v>
+        <v>57651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyran- Strycktjärn, Nb</t>
+          <t>Långmyran, Strycktjärn, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>784333</v>
+        <v>784312</v>
       </c>
       <c r="R13" t="n">
-        <v>7286210</v>
+        <v>7286305</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1877,14 +1872,19 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gran bark kvar</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,12 +1899,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -4178,10 +4178,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125201636</v>
+        <v>125201663</v>
       </c>
       <c r="B37" t="n">
-        <v>75066</v>
+        <v>82779</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4189,21 +4189,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>784334</v>
+        <v>784333</v>
       </c>
       <c r="R37" t="n">
-        <v>7286242</v>
+        <v>7286405</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125201663</v>
+        <v>125201636</v>
       </c>
       <c r="B38" t="n">
-        <v>82779</v>
+        <v>75066</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4286,21 +4286,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>784333</v>
+        <v>784334</v>
       </c>
       <c r="R38" t="n">
-        <v>7286405</v>
+        <v>7286242</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5541,32 +5541,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125201639</v>
+        <v>125201640</v>
       </c>
       <c r="B51" t="n">
-        <v>91192</v>
+        <v>91227</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>784305</v>
+        <v>784265</v>
       </c>
       <c r="R51" t="n">
-        <v>7286333</v>
+        <v>7286257</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125201640</v>
+        <v>125201641</v>
       </c>
       <c r="B52" t="n">
         <v>91227</v>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>784265</v>
+        <v>784273</v>
       </c>
       <c r="R52" t="n">
-        <v>7286257</v>
+        <v>7286260</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125201641</v>
+        <v>125201666</v>
       </c>
       <c r="B53" t="n">
-        <v>91227</v>
+        <v>82779</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>784273</v>
+        <v>784339</v>
       </c>
       <c r="R53" t="n">
-        <v>7286260</v>
+        <v>7286244</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5832,32 +5832,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125201666</v>
+        <v>125201639</v>
       </c>
       <c r="B54" t="n">
-        <v>82779</v>
+        <v>91192</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>784339</v>
+        <v>784305</v>
       </c>
       <c r="R54" t="n">
-        <v>7286244</v>
+        <v>7286333</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -3502,7 +3502,7 @@
         <v>125201671</v>
       </c>
       <c r="B30" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>125201678</v>
       </c>
       <c r="B31" t="n">
-        <v>96457</v>
+        <v>96460</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>125201679</v>
       </c>
       <c r="B32" t="n">
-        <v>96457</v>
+        <v>96460</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>125201670</v>
       </c>
       <c r="B33" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>125201644</v>
       </c>
       <c r="B34" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>125201668</v>
       </c>
       <c r="B35" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>125201645</v>
       </c>
       <c r="B36" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>125201663</v>
       </c>
       <c r="B37" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>125201636</v>
       </c>
       <c r="B38" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>125201635</v>
       </c>
       <c r="B39" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4474,32 +4474,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125201655</v>
+        <v>125201657</v>
       </c>
       <c r="B40" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>784464</v>
+        <v>784313</v>
       </c>
       <c r="R40" t="n">
-        <v>7286450</v>
+        <v>7286311</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4571,32 +4571,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125201657</v>
+        <v>125201655</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>98334</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>784313</v>
+        <v>784464</v>
       </c>
       <c r="R41" t="n">
-        <v>7286311</v>
+        <v>7286450</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4671,7 +4671,7 @@
         <v>125201664</v>
       </c>
       <c r="B42" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>125201637</v>
       </c>
       <c r="B43" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>125201656</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>125201646</v>
       </c>
       <c r="B45" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>125201659</v>
       </c>
       <c r="B46" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>125201660</v>
       </c>
       <c r="B47" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>125201661</v>
       </c>
       <c r="B48" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>125201650</v>
       </c>
       <c r="B49" t="n">
-        <v>91520</v>
+        <v>91524</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>125201642</v>
       </c>
       <c r="B50" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>125201640</v>
       </c>
       <c r="B51" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5638,32 +5638,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125201641</v>
+        <v>125201639</v>
       </c>
       <c r="B52" t="n">
-        <v>91227</v>
+        <v>91193</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>784273</v>
+        <v>784305</v>
       </c>
       <c r="R52" t="n">
-        <v>7286260</v>
+        <v>7286333</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125201666</v>
+        <v>125201641</v>
       </c>
       <c r="B53" t="n">
-        <v>82779</v>
+        <v>91228</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>784339</v>
+        <v>784273</v>
       </c>
       <c r="R53" t="n">
-        <v>7286244</v>
+        <v>7286260</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5832,32 +5832,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125201639</v>
+        <v>125201666</v>
       </c>
       <c r="B54" t="n">
-        <v>91192</v>
+        <v>82780</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>784305</v>
+        <v>784339</v>
       </c>
       <c r="R54" t="n">
-        <v>7286333</v>
+        <v>7286244</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -5347,10 +5347,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125201650</v>
+        <v>125201642</v>
       </c>
       <c r="B49" t="n">
-        <v>91524</v>
+        <v>91228</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5358,21 +5358,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>784257</v>
+        <v>784349</v>
       </c>
       <c r="R49" t="n">
-        <v>7286240</v>
+        <v>7286343</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5444,10 +5444,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125201642</v>
+        <v>125201650</v>
       </c>
       <c r="B50" t="n">
-        <v>91228</v>
+        <v>91524</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5455,21 +5455,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>784349</v>
+        <v>784257</v>
       </c>
       <c r="R50" t="n">
-        <v>7286343</v>
+        <v>7286240</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -3502,7 +3502,7 @@
         <v>125201671</v>
       </c>
       <c r="B30" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>125201678</v>
       </c>
       <c r="B31" t="n">
-        <v>96460</v>
+        <v>96464</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>125201679</v>
       </c>
       <c r="B32" t="n">
-        <v>96460</v>
+        <v>96464</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>125201670</v>
       </c>
       <c r="B33" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>125201644</v>
       </c>
       <c r="B34" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>125201668</v>
       </c>
       <c r="B35" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>125201645</v>
       </c>
       <c r="B36" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4178,10 +4178,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125201663</v>
+        <v>125201636</v>
       </c>
       <c r="B37" t="n">
-        <v>82780</v>
+        <v>75067</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4189,21 +4189,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>784333</v>
+        <v>784334</v>
       </c>
       <c r="R37" t="n">
-        <v>7286405</v>
+        <v>7286242</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125201636</v>
+        <v>125201663</v>
       </c>
       <c r="B38" t="n">
-        <v>75067</v>
+        <v>82784</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4286,21 +4286,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>784334</v>
+        <v>784333</v>
       </c>
       <c r="R38" t="n">
-        <v>7286242</v>
+        <v>7286405</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4477,7 +4477,7 @@
         <v>125201657</v>
       </c>
       <c r="B40" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>125201655</v>
       </c>
       <c r="B41" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>125201664</v>
       </c>
       <c r="B42" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>125201656</v>
       </c>
       <c r="B44" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>125201646</v>
       </c>
       <c r="B45" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>125201659</v>
       </c>
       <c r="B46" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>125201660</v>
       </c>
       <c r="B47" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>125201661</v>
       </c>
       <c r="B48" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>125201642</v>
       </c>
       <c r="B49" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>125201650</v>
       </c>
       <c r="B50" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5541,32 +5541,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125201640</v>
+        <v>125201639</v>
       </c>
       <c r="B51" t="n">
-        <v>91228</v>
+        <v>91197</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>784265</v>
+        <v>784305</v>
       </c>
       <c r="R51" t="n">
-        <v>7286257</v>
+        <v>7286333</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5638,32 +5638,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125201639</v>
+        <v>125201640</v>
       </c>
       <c r="B52" t="n">
-        <v>91193</v>
+        <v>91232</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>784305</v>
+        <v>784265</v>
       </c>
       <c r="R52" t="n">
-        <v>7286333</v>
+        <v>7286257</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5738,7 +5738,7 @@
         <v>125201641</v>
       </c>
       <c r="B53" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>125201666</v>
       </c>
       <c r="B54" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -4474,32 +4474,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125201657</v>
+        <v>125201655</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>98338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>784313</v>
+        <v>784464</v>
       </c>
       <c r="R40" t="n">
-        <v>7286311</v>
+        <v>7286450</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4571,32 +4571,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125201655</v>
+        <v>125201657</v>
       </c>
       <c r="B41" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>784464</v>
+        <v>784313</v>
       </c>
       <c r="R41" t="n">
-        <v>7286450</v>
+        <v>7286311</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 23597-2025 artfynd.xlsx
+++ b/artfynd/A 23597-2025 artfynd.xlsx
@@ -4178,10 +4178,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125201636</v>
+        <v>125201663</v>
       </c>
       <c r="B37" t="n">
-        <v>75067</v>
+        <v>82784</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4189,21 +4189,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>784334</v>
+        <v>784333</v>
       </c>
       <c r="R37" t="n">
-        <v>7286242</v>
+        <v>7286405</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125201663</v>
+        <v>125201636</v>
       </c>
       <c r="B38" t="n">
-        <v>82784</v>
+        <v>75067</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4286,21 +4286,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>784333</v>
+        <v>784334</v>
       </c>
       <c r="R38" t="n">
-        <v>7286405</v>
+        <v>7286242</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4477,7 +4477,7 @@
         <v>125201655</v>
       </c>
       <c r="B40" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5347,10 +5347,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125201642</v>
+        <v>125201650</v>
       </c>
       <c r="B49" t="n">
-        <v>91232</v>
+        <v>91528</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5358,21 +5358,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>784349</v>
+        <v>784257</v>
       </c>
       <c r="R49" t="n">
-        <v>7286343</v>
+        <v>7286240</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5444,10 +5444,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125201650</v>
+        <v>125201642</v>
       </c>
       <c r="B50" t="n">
-        <v>91528</v>
+        <v>91232</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5455,21 +5455,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>784257</v>
+        <v>784349</v>
       </c>
       <c r="R50" t="n">
-        <v>7286240</v>
+        <v>7286343</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5541,32 +5541,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125201639</v>
+        <v>125201640</v>
       </c>
       <c r="B51" t="n">
-        <v>91197</v>
+        <v>91232</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>784305</v>
+        <v>784265</v>
       </c>
       <c r="R51" t="n">
-        <v>7286333</v>
+        <v>7286257</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5638,32 +5638,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125201640</v>
+        <v>125201639</v>
       </c>
       <c r="B52" t="n">
-        <v>91232</v>
+        <v>91197</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>784265</v>
+        <v>784305</v>
       </c>
       <c r="R52" t="n">
-        <v>7286257</v>
+        <v>7286333</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
